--- a/docs/光和稼働データ収集装置デバイスマップ.xlsx
+++ b/docs/光和稼働データ収集装置デバイスマップ.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myProgram\GitHub\ForMitsuwa\factory_visualize_server_atmw\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72254C67-CF45-497A-9E26-BAB1D80713D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD1138D1-3B40-4B31-9099-814B526CD1F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="11520" windowHeight="12360" xr2:uid="{2B542973-F752-4A81-A420-BFC37E5D0A51}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{2B542973-F752-4A81-A420-BFC37E5D0A51}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="旧割付" sheetId="1" r:id="rId1"/>
+    <sheet name="20260622" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="722" uniqueCount="568">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1718" uniqueCount="753">
   <si>
     <t>ZF0</t>
     <phoneticPr fontId="1"/>
@@ -1975,6 +1976,589 @@
       <t>ハイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DM400</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DM401</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VTステータス表示デバイス</t>
+    <rPh sb="7" eb="9">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DM402</t>
+  </si>
+  <si>
+    <t>DM403</t>
+  </si>
+  <si>
+    <t>DM404</t>
+  </si>
+  <si>
+    <t>DM405</t>
+  </si>
+  <si>
+    <t>DM406</t>
+  </si>
+  <si>
+    <t>DM407</t>
+  </si>
+  <si>
+    <t>DM408</t>
+  </si>
+  <si>
+    <t>DM409</t>
+  </si>
+  <si>
+    <t>DM410</t>
+  </si>
+  <si>
+    <t>DM411</t>
+  </si>
+  <si>
+    <t>DM412</t>
+  </si>
+  <si>
+    <t>DM413</t>
+  </si>
+  <si>
+    <t>DM414</t>
+  </si>
+  <si>
+    <t>DM415</t>
+  </si>
+  <si>
+    <t>DM416</t>
+  </si>
+  <si>
+    <t>DM417</t>
+  </si>
+  <si>
+    <t>DM418</t>
+  </si>
+  <si>
+    <t>DM419</t>
+  </si>
+  <si>
+    <t>DM420</t>
+  </si>
+  <si>
+    <t>DM421</t>
+  </si>
+  <si>
+    <t>DM422</t>
+  </si>
+  <si>
+    <t>DM423</t>
+  </si>
+  <si>
+    <t>DM424</t>
+  </si>
+  <si>
+    <t>DM425</t>
+  </si>
+  <si>
+    <t>DM426</t>
+  </si>
+  <si>
+    <t>DM427</t>
+  </si>
+  <si>
+    <t>DM428</t>
+  </si>
+  <si>
+    <t>DM429</t>
+  </si>
+  <si>
+    <t>DM430</t>
+  </si>
+  <si>
+    <t>DM431</t>
+  </si>
+  <si>
+    <t>DM432</t>
+  </si>
+  <si>
+    <t>DM433</t>
+  </si>
+  <si>
+    <t>DM434</t>
+  </si>
+  <si>
+    <t>DM435</t>
+  </si>
+  <si>
+    <t>DM436</t>
+  </si>
+  <si>
+    <t>DM437</t>
+  </si>
+  <si>
+    <t>DM438</t>
+  </si>
+  <si>
+    <t>DM439</t>
+  </si>
+  <si>
+    <t>DM440</t>
+  </si>
+  <si>
+    <t>DM441</t>
+  </si>
+  <si>
+    <t>DM442</t>
+  </si>
+  <si>
+    <t>DM443</t>
+  </si>
+  <si>
+    <t>DM444</t>
+  </si>
+  <si>
+    <t>DM445</t>
+  </si>
+  <si>
+    <t>DM446</t>
+  </si>
+  <si>
+    <t>DM447</t>
+  </si>
+  <si>
+    <t>DM448</t>
+  </si>
+  <si>
+    <t>DM449</t>
+  </si>
+  <si>
+    <t>36号機</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>46号機</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>47号機</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>48号機</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>49号機</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>50号機</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>63号機</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>45号機</t>
+    <rPh sb="2" eb="4">
+      <t>ゴウキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>57号機</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>53号機</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>54号機</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Block50</t>
+  </si>
+  <si>
+    <t>Block51</t>
+  </si>
+  <si>
+    <t>Block52</t>
+  </si>
+  <si>
+    <t>Block53</t>
+  </si>
+  <si>
+    <t>Block54</t>
+  </si>
+  <si>
+    <t>Block55</t>
+  </si>
+  <si>
+    <t>Block56</t>
+  </si>
+  <si>
+    <t>Block57</t>
+  </si>
+  <si>
+    <t>Block58</t>
+  </si>
+  <si>
+    <t>Block59</t>
+  </si>
+  <si>
+    <t>Block60</t>
+  </si>
+  <si>
+    <t>DM450</t>
+  </si>
+  <si>
+    <t>DM451</t>
+  </si>
+  <si>
+    <t>DM452</t>
+  </si>
+  <si>
+    <t>DM453</t>
+  </si>
+  <si>
+    <t>DM454</t>
+  </si>
+  <si>
+    <t>DM455</t>
+  </si>
+  <si>
+    <t>DM456</t>
+  </si>
+  <si>
+    <t>DM457</t>
+  </si>
+  <si>
+    <t>DM458</t>
+  </si>
+  <si>
+    <t>DM459</t>
+  </si>
+  <si>
+    <t>DM460</t>
+  </si>
+  <si>
+    <t>64号機</t>
+    <rPh sb="2" eb="4">
+      <t>ゴウキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>52号機</t>
+    <rPh sb="2" eb="4">
+      <t>ゴウキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DM23000</t>
+  </si>
+  <si>
+    <t>DM23060</t>
+  </si>
+  <si>
+    <t>DM23120</t>
+  </si>
+  <si>
+    <t>DM23180</t>
+  </si>
+  <si>
+    <t>DM23240</t>
+  </si>
+  <si>
+    <t>DM23300</t>
+  </si>
+  <si>
+    <t>DM23360</t>
+  </si>
+  <si>
+    <t>DM23420</t>
+  </si>
+  <si>
+    <t>DM23480</t>
+  </si>
+  <si>
+    <t>DM23540</t>
+  </si>
+  <si>
+    <t>DM23600</t>
+  </si>
+  <si>
+    <t>DM23059</t>
+  </si>
+  <si>
+    <t>DM23119</t>
+  </si>
+  <si>
+    <t>DM23179</t>
+  </si>
+  <si>
+    <t>DM23239</t>
+  </si>
+  <si>
+    <t>DM23299</t>
+  </si>
+  <si>
+    <t>DM23359</t>
+  </si>
+  <si>
+    <t>DM23419</t>
+  </si>
+  <si>
+    <t>DM23479</t>
+  </si>
+  <si>
+    <t>DM23539</t>
+  </si>
+  <si>
+    <t>DM23599</t>
+  </si>
+  <si>
+    <t>DM23659</t>
+  </si>
+  <si>
+    <t>ZF75010</t>
+  </si>
+  <si>
+    <t>ZF76510</t>
+  </si>
+  <si>
+    <t>ZF78010</t>
+  </si>
+  <si>
+    <t>ZF79510</t>
+  </si>
+  <si>
+    <t>ZF81010</t>
+  </si>
+  <si>
+    <t>ZF82510</t>
+  </si>
+  <si>
+    <t>ZF84010</t>
+  </si>
+  <si>
+    <t>ZF85510</t>
+  </si>
+  <si>
+    <t>ZF87010</t>
+  </si>
+  <si>
+    <t>ZF88510</t>
+  </si>
+  <si>
+    <t>ZF90010</t>
+  </si>
+  <si>
+    <t>ZF76209</t>
+  </si>
+  <si>
+    <t>ZF77709</t>
+  </si>
+  <si>
+    <t>ZF79209</t>
+  </si>
+  <si>
+    <t>ZF80709</t>
+  </si>
+  <si>
+    <t>ZF82209</t>
+  </si>
+  <si>
+    <t>ZF83709</t>
+  </si>
+  <si>
+    <t>ZF85209</t>
+  </si>
+  <si>
+    <t>ZF86709</t>
+  </si>
+  <si>
+    <t>ZF88209</t>
+  </si>
+  <si>
+    <t>ZF89709</t>
+  </si>
+  <si>
+    <t>ZF91209</t>
+  </si>
+  <si>
+    <t>ZF76210</t>
+  </si>
+  <si>
+    <t>ZF77710</t>
+  </si>
+  <si>
+    <t>ZF79210</t>
+  </si>
+  <si>
+    <t>ZF80710</t>
+  </si>
+  <si>
+    <t>ZF82210</t>
+  </si>
+  <si>
+    <t>ZF83710</t>
+  </si>
+  <si>
+    <t>ZF85210</t>
+  </si>
+  <si>
+    <t>ZF86710</t>
+  </si>
+  <si>
+    <t>ZF88210</t>
+  </si>
+  <si>
+    <t>ZF89710</t>
+  </si>
+  <si>
+    <t>ZF91210</t>
+  </si>
+  <si>
+    <t>ZF76449</t>
+  </si>
+  <si>
+    <t>ZF77949</t>
+  </si>
+  <si>
+    <t>ZF79449</t>
+  </si>
+  <si>
+    <t>ZF80949</t>
+  </si>
+  <si>
+    <t>ZF82449</t>
+  </si>
+  <si>
+    <t>ZF83949</t>
+  </si>
+  <si>
+    <t>ZF85449</t>
+  </si>
+  <si>
+    <t>ZF86949</t>
+  </si>
+  <si>
+    <t>ZF88449</t>
+  </si>
+  <si>
+    <t>ZF89949</t>
+  </si>
+  <si>
+    <t>ZF91449</t>
+  </si>
+  <si>
+    <t>ZF75000</t>
+  </si>
+  <si>
+    <t>ZF76500</t>
+  </si>
+  <si>
+    <t>ZF78000</t>
+  </si>
+  <si>
+    <t>ZF79500</t>
+  </si>
+  <si>
+    <t>ZF81000</t>
+  </si>
+  <si>
+    <t>ZF82500</t>
+  </si>
+  <si>
+    <t>ZF84000</t>
+  </si>
+  <si>
+    <t>ZF85500</t>
+  </si>
+  <si>
+    <t>ZF87000</t>
+  </si>
+  <si>
+    <t>ZF88500</t>
+  </si>
+  <si>
+    <t>ZF90000</t>
+  </si>
+  <si>
+    <t>ZF75002</t>
+  </si>
+  <si>
+    <t>ZF76502</t>
+  </si>
+  <si>
+    <t>ZF78002</t>
+  </si>
+  <si>
+    <t>ZF79502</t>
+  </si>
+  <si>
+    <t>ZF81002</t>
+  </si>
+  <si>
+    <t>ZF82502</t>
+  </si>
+  <si>
+    <t>ZF84002</t>
+  </si>
+  <si>
+    <t>ZF85502</t>
+  </si>
+  <si>
+    <t>ZF87002</t>
+  </si>
+  <si>
+    <t>ZF88502</t>
+  </si>
+  <si>
+    <t>ZF90002</t>
+  </si>
+  <si>
+    <t>ZF75003</t>
+  </si>
+  <si>
+    <t>ZF76503</t>
+  </si>
+  <si>
+    <t>ZF78003</t>
+  </si>
+  <si>
+    <t>ZF79503</t>
+  </si>
+  <si>
+    <t>ZF81003</t>
+  </si>
+  <si>
+    <t>ZF82503</t>
+  </si>
+  <si>
+    <t>ZF84003</t>
+  </si>
+  <si>
+    <t>ZF85503</t>
+  </si>
+  <si>
+    <t>ZF87003</t>
+  </si>
+  <si>
+    <t>ZF88503</t>
+  </si>
+  <si>
+    <t>ZF90003</t>
   </si>
 </sst>
 </file>
@@ -2138,7 +2722,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2202,11 +2786,39 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="4">
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="medium">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="medium">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="medium">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -2248,9 +2860,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8383A00C-C06B-477B-9A4B-14E933CB3CFE}" name="テーブル22" displayName="テーブル22" ref="B2:AZ18" totalsRowShown="0" tableBorderDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8383A00C-C06B-477B-9A4B-14E933CB3CFE}" name="テーブル22" displayName="テーブル22" ref="B2:AZ18" totalsRowShown="0" tableBorderDxfId="3">
   <tableColumns count="51">
-    <tableColumn id="1" xr3:uid="{E7B7D901-75C1-4740-B690-4FE5404CF2F1}" name=" 各カウンタ(日付変更時更新)" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{E7B7D901-75C1-4740-B690-4FE5404CF2F1}" name=" 各カウンタ(日付変更時更新)" dataDxfId="2"/>
     <tableColumn id="2" xr3:uid="{72363EDE-2713-42C2-8D15-40A4D772076E}" name="Block0"/>
     <tableColumn id="3" xr3:uid="{6EF783C4-01DD-4CA6-87D1-7F51D32DD8E0}" name="Block1"/>
     <tableColumn id="4" xr3:uid="{B9340072-0A67-4C05-8935-7945A7C76A95}" name="Block2"/>
@@ -2301,6 +2913,76 @@
     <tableColumn id="63" xr3:uid="{F0D93B95-F9CE-4A71-9ADD-434B950E24A5}" name="Block47"/>
     <tableColumn id="62" xr3:uid="{5D7DA81B-821D-4A19-BB85-F4697131F106}" name="Block48"/>
     <tableColumn id="9" xr3:uid="{2FCE56B6-0415-40C6-9281-5D9880712E0C}" name="Block49"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight18" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{6DEC4304-1BD1-49A7-AE1B-D1BB7080F0E6}" name="テーブル223" displayName="テーブル223" ref="B2:BK18" totalsRowShown="0" tableBorderDxfId="1">
+  <tableColumns count="62">
+    <tableColumn id="1" xr3:uid="{39BBD529-BEC1-46A6-AD6B-FDCD6EB2D0E9}" name=" 各カウンタ(日付変更時更新)" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{910B3ABA-A8EF-46B0-94A9-6A12DD9D9C92}" name="Block0"/>
+    <tableColumn id="3" xr3:uid="{1FE8F4C6-1B44-43FA-9803-44CD252D7985}" name="Block1"/>
+    <tableColumn id="4" xr3:uid="{94BB05A7-9464-4C96-8E35-B6DDB289D1FD}" name="Block2"/>
+    <tableColumn id="5" xr3:uid="{D6370DB2-AAD9-4B7B-BD5D-C1D76EA6954A}" name="Block3"/>
+    <tableColumn id="6" xr3:uid="{FB22429F-54D6-4433-9B33-817B5AF05621}" name="Block4"/>
+    <tableColumn id="7" xr3:uid="{53F6B16A-156C-4BD0-A71C-7C92C8AB1830}" name="Block5"/>
+    <tableColumn id="10" xr3:uid="{BD300253-20D2-4BBD-BF59-33618454043C}" name="Block6"/>
+    <tableColumn id="11" xr3:uid="{C7FC0F38-1E97-48BB-A5D4-A17AE4E71A1B}" name="Block7"/>
+    <tableColumn id="12" xr3:uid="{A007A4FC-B646-4AB0-A883-44CCD3E6285B}" name="Block8"/>
+    <tableColumn id="13" xr3:uid="{8023DD18-8819-4EB6-A092-C23423094788}" name="Block9"/>
+    <tableColumn id="14" xr3:uid="{A339B744-6AFC-4ABB-B520-056E8575C930}" name="Block10"/>
+    <tableColumn id="15" xr3:uid="{AF1E75B7-A2C1-4132-95A5-51671B2E4879}" name="Block11"/>
+    <tableColumn id="16" xr3:uid="{7716E508-3FC3-4CFE-9E9F-6F3F0DED4BDA}" name="Block12"/>
+    <tableColumn id="17" xr3:uid="{3B762120-A8AC-4984-AEE0-0C378F3F0CB1}" name="Block13"/>
+    <tableColumn id="18" xr3:uid="{31CB52AF-4ADF-48F0-9851-31A1F8252EBB}" name="Block14"/>
+    <tableColumn id="19" xr3:uid="{9FCEE9EA-D241-43A6-A1F3-255FF0610A00}" name="Block15"/>
+    <tableColumn id="20" xr3:uid="{439B17CF-1FFA-4680-81A7-F9828816F7AC}" name="Block16"/>
+    <tableColumn id="21" xr3:uid="{50C9443B-5C32-4484-8013-C9C319B10563}" name="Block17"/>
+    <tableColumn id="22" xr3:uid="{354716D2-1A5E-4A49-AA19-DC2D67654657}" name="Block18"/>
+    <tableColumn id="23" xr3:uid="{E11B56EF-9C6D-4572-810F-17AB383B3CAE}" name="Block19"/>
+    <tableColumn id="24" xr3:uid="{69CD2830-A4A7-405D-B1C7-E63219E125F3}" name="Block20"/>
+    <tableColumn id="25" xr3:uid="{AD153AF8-402B-4545-B0AD-5AAA5B1BC2FC}" name="Block21"/>
+    <tableColumn id="26" xr3:uid="{ADAD1A33-8FAF-4F94-B00F-18E3F48A7DAD}" name="Block22"/>
+    <tableColumn id="27" xr3:uid="{97F895E7-78B7-406A-A20C-3B75F76C919A}" name="Block23"/>
+    <tableColumn id="28" xr3:uid="{596E44E0-CA9E-48B3-8936-855305A52BBD}" name="Block24"/>
+    <tableColumn id="29" xr3:uid="{DC9FD921-6067-49FE-83D4-5A116264F7E4}" name="Block25"/>
+    <tableColumn id="30" xr3:uid="{79883C44-4623-4ED6-A1F5-0D4B9157A573}" name="Block26"/>
+    <tableColumn id="31" xr3:uid="{A44CC969-7CEB-4CEB-B0A3-8277541D0220}" name="Block27"/>
+    <tableColumn id="32" xr3:uid="{ABFC4B51-93DA-407D-87E4-5A3FFB8719A5}" name="Block28"/>
+    <tableColumn id="33" xr3:uid="{21BBFBDF-FC6B-48AB-956A-FDCACFEB1832}" name="Block29"/>
+    <tableColumn id="34" xr3:uid="{36CA6B73-DE51-4C79-8D95-A4FA8EB09F5E}" name="Block30"/>
+    <tableColumn id="35" xr3:uid="{021A3A00-E235-4FC0-93D7-4A3DE5E7C3ED}" name="Block31"/>
+    <tableColumn id="36" xr3:uid="{028E0C9D-2F50-41DD-A6C5-98891125DC38}" name="Block32"/>
+    <tableColumn id="37" xr3:uid="{8B8B990E-D3CF-4580-BE0D-573872171A14}" name="Block33"/>
+    <tableColumn id="38" xr3:uid="{B7B3C7E9-6C7A-4B41-B262-1A59C1432C0D}" name="Block34"/>
+    <tableColumn id="39" xr3:uid="{4A5A895A-6BF7-408B-BE8D-8DD934D1EA2B}" name="Block35"/>
+    <tableColumn id="40" xr3:uid="{830E66C2-EA7A-40A2-8D11-3B2614484402}" name="Block36"/>
+    <tableColumn id="41" xr3:uid="{98B518E8-19D1-4C7C-950E-400BEC843DAC}" name="Block37"/>
+    <tableColumn id="42" xr3:uid="{A17F4E9E-429E-4352-90EC-EE0981BC4094}" name="Block38"/>
+    <tableColumn id="43" xr3:uid="{DE910F14-B87A-4394-BD10-B4C9918A0C9E}" name="Block39"/>
+    <tableColumn id="51" xr3:uid="{073F9370-B456-4E31-8BDB-B7C6FAE4CAFE}" name="Block40"/>
+    <tableColumn id="56" xr3:uid="{FDD46D66-A55C-49EB-A1B9-1592F797068C}" name="Block41"/>
+    <tableColumn id="68" xr3:uid="{0BF05BD7-A4C5-49C4-BC15-5155906BE192}" name="Block42"/>
+    <tableColumn id="67" xr3:uid="{B13436A6-31CE-4C5B-AA6E-BA75E586FF64}" name="Block43"/>
+    <tableColumn id="66" xr3:uid="{69969659-BEF5-4150-8371-E40837BD4675}" name="Block44"/>
+    <tableColumn id="65" xr3:uid="{E9D999F9-9505-4D18-84DF-401E24DD050A}" name="Block45"/>
+    <tableColumn id="64" xr3:uid="{9EE6C05E-00F0-4049-A5D4-DBDAAAF2AAFE}" name="Block46"/>
+    <tableColumn id="63" xr3:uid="{D14FF828-BAE9-427C-AB80-33E45CB5E575}" name="Block47"/>
+    <tableColumn id="62" xr3:uid="{DEF9BA2E-6944-435C-84D2-51B5B3324B8E}" name="Block48"/>
+    <tableColumn id="9" xr3:uid="{30C60DEF-BE98-4A58-9449-5FB370F2D4EE}" name="Block49"/>
+    <tableColumn id="8" xr3:uid="{721C0EEB-8272-40B1-BA24-0A6C475A1162}" name="Block50"/>
+    <tableColumn id="44" xr3:uid="{1AC139D1-B877-447C-B355-7227F9D5772C}" name="Block51"/>
+    <tableColumn id="45" xr3:uid="{84E1FAAD-3ED8-4AE6-9F03-D0EF1D830533}" name="Block52"/>
+    <tableColumn id="46" xr3:uid="{27F4CCE0-282E-4336-AE98-68A1B8A04B50}" name="Block53"/>
+    <tableColumn id="47" xr3:uid="{DC2F9BEE-66C1-4A3E-B614-D74F67FDF8E7}" name="Block54"/>
+    <tableColumn id="48" xr3:uid="{F7D5DC16-2A34-45F9-9CD2-F366A176DAA9}" name="Block55"/>
+    <tableColumn id="49" xr3:uid="{450BC5CF-7444-49AD-A648-CE13E05F1812}" name="Block56"/>
+    <tableColumn id="50" xr3:uid="{7B37BFA2-32E5-4802-B8E0-95A5B41E3FF0}" name="Block57"/>
+    <tableColumn id="52" xr3:uid="{4165E52B-E2EE-451B-BE2B-ED678B27B2F6}" name="Block58"/>
+    <tableColumn id="53" xr3:uid="{49CF6FE6-1734-4D24-A4FA-48295D36AD0E}" name="Block59"/>
+    <tableColumn id="54" xr3:uid="{B01DA723-31E3-4AC1-9F08-11BA23308B28}" name="Block60"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight18" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2603,14 +3285,169 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62123ED-9C66-404D-AD1C-3CC6E3D9A234}">
-  <dimension ref="B2:AZ32"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <dimension ref="B1:AZ32"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="32" bestFit="1" customWidth="1"/>
-    <col min="3" max="52" width="9.69921875" customWidth="1"/>
+    <col min="3" max="52" width="9.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:52" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:52" x14ac:dyDescent="0.4">
+      <c r="B1" t="s">
+        <v>570</v>
+      </c>
+      <c r="C1" t="s">
+        <v>568</v>
+      </c>
+      <c r="D1" t="s">
+        <v>569</v>
+      </c>
+      <c r="E1" t="s">
+        <v>571</v>
+      </c>
+      <c r="F1" t="s">
+        <v>572</v>
+      </c>
+      <c r="G1" t="s">
+        <v>573</v>
+      </c>
+      <c r="H1" t="s">
+        <v>574</v>
+      </c>
+      <c r="I1" t="s">
+        <v>575</v>
+      </c>
+      <c r="J1" t="s">
+        <v>576</v>
+      </c>
+      <c r="K1" t="s">
+        <v>577</v>
+      </c>
+      <c r="L1" t="s">
+        <v>578</v>
+      </c>
+      <c r="M1" t="s">
+        <v>579</v>
+      </c>
+      <c r="N1" t="s">
+        <v>580</v>
+      </c>
+      <c r="O1" t="s">
+        <v>581</v>
+      </c>
+      <c r="P1" t="s">
+        <v>582</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>583</v>
+      </c>
+      <c r="R1" t="s">
+        <v>584</v>
+      </c>
+      <c r="S1" t="s">
+        <v>585</v>
+      </c>
+      <c r="T1" t="s">
+        <v>586</v>
+      </c>
+      <c r="U1" t="s">
+        <v>587</v>
+      </c>
+      <c r="V1" t="s">
+        <v>588</v>
+      </c>
+      <c r="W1" t="s">
+        <v>589</v>
+      </c>
+      <c r="X1" t="s">
+        <v>590</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>591</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>592</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>593</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>594</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>595</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>596</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>597</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>598</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>599</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>600</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>601</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>602</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>603</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>604</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>605</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>606</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>607</v>
+      </c>
+      <c r="AP1" t="s">
+        <v>608</v>
+      </c>
+      <c r="AQ1" t="s">
+        <v>609</v>
+      </c>
+      <c r="AR1" t="s">
+        <v>610</v>
+      </c>
+      <c r="AS1" t="s">
+        <v>611</v>
+      </c>
+      <c r="AT1" t="s">
+        <v>612</v>
+      </c>
+      <c r="AU1" t="s">
+        <v>613</v>
+      </c>
+      <c r="AV1" t="s">
+        <v>614</v>
+      </c>
+      <c r="AW1" t="s">
+        <v>615</v>
+      </c>
+      <c r="AX1" t="s">
+        <v>616</v>
+      </c>
+      <c r="AY1" t="s">
+        <v>617</v>
+      </c>
+      <c r="AZ1" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="2" spans="2:52" x14ac:dyDescent="0.4">
       <c r="B2" s="4" t="s">
         <v>38</v>
       </c>
@@ -2765,7 +3602,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="3" spans="2:52" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:52" x14ac:dyDescent="0.4">
       <c r="B3" s="4" t="s">
         <v>66</v>
       </c>
@@ -2823,10 +3660,10 @@
       <c r="T3" s="10" t="s">
         <v>537</v>
       </c>
-      <c r="U3" s="13" t="s">
+      <c r="U3" s="10" t="s">
         <v>561</v>
       </c>
-      <c r="V3" s="13" t="s">
+      <c r="V3" s="10" t="s">
         <v>561</v>
       </c>
       <c r="W3" s="10" t="s">
@@ -2898,6 +3735,7 @@
       <c r="AS3" s="10" t="s">
         <v>560</v>
       </c>
+      <c r="AT3" s="10"/>
       <c r="AU3" s="10"/>
       <c r="AV3" s="10"/>
       <c r="AW3" s="10"/>
@@ -2905,7 +3743,7 @@
       <c r="AY3" s="10"/>
       <c r="AZ3" s="10"/>
     </row>
-    <row r="4" spans="2:52" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:52" x14ac:dyDescent="0.4">
       <c r="B4" s="1" t="s">
         <v>33</v>
       </c>
@@ -3060,7 +3898,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="2:52" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:52" x14ac:dyDescent="0.4">
       <c r="B5" s="1" t="s">
         <v>23</v>
       </c>
@@ -3215,7 +4053,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="2:52" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:52" x14ac:dyDescent="0.4">
       <c r="B6" s="1" t="s">
         <v>24</v>
       </c>
@@ -3370,12 +4208,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="2:52" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:52" x14ac:dyDescent="0.4">
       <c r="B8" s="3" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="9" spans="2:52" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:52" x14ac:dyDescent="0.4">
       <c r="B9" s="2" t="s">
         <v>52</v>
       </c>
@@ -3530,7 +4368,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="10" spans="2:52" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:52" x14ac:dyDescent="0.4">
       <c r="B10" s="1"/>
       <c r="C10" t="s">
         <v>3</v>
@@ -3683,7 +4521,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="2:52" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:52" x14ac:dyDescent="0.4">
       <c r="B11" s="2"/>
       <c r="C11" t="s">
         <v>43</v>
@@ -3836,10 +4674,10 @@
         <v>335</v>
       </c>
     </row>
-    <row r="12" spans="2:52" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:52" x14ac:dyDescent="0.4">
       <c r="B12" s="2"/>
     </row>
-    <row r="13" spans="2:52" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:52" x14ac:dyDescent="0.4">
       <c r="B13" s="2">
         <v>0.16666666666666666</v>
       </c>
@@ -3994,7 +4832,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="14" spans="2:52" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:52" x14ac:dyDescent="0.4">
       <c r="B14" s="1" t="s">
         <v>3</v>
       </c>
@@ -4149,7 +4987,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="2:52" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:52" x14ac:dyDescent="0.4">
       <c r="B15" s="2">
         <v>0.99930555555555556</v>
       </c>
@@ -4304,7 +5142,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="16" spans="2:52" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:52" x14ac:dyDescent="0.4">
       <c r="B16" s="2">
         <v>0</v>
       </c>
@@ -4459,7 +5297,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="17" spans="2:52" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:52" x14ac:dyDescent="0.4">
       <c r="B17" s="1" t="s">
         <v>3</v>
       </c>
@@ -4614,7 +5452,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="2:52" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:52" x14ac:dyDescent="0.4">
       <c r="B18" s="2">
         <v>0.16597222222222222</v>
       </c>
@@ -4769,14 +5607,14 @@
         <v>423</v>
       </c>
     </row>
-    <row r="20" spans="2:52" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:52" x14ac:dyDescent="0.4">
       <c r="B20" s="9" t="s">
         <v>54</v>
       </c>
       <c r="C20" s="7"/>
       <c r="D20" s="14"/>
     </row>
-    <row r="21" spans="2:52" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:52" x14ac:dyDescent="0.4">
       <c r="B21" s="11" t="s">
         <v>55</v>
       </c>
@@ -4787,7 +5625,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="22" spans="2:52" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:52" x14ac:dyDescent="0.4">
       <c r="B22" s="11" t="s">
         <v>56</v>
       </c>
@@ -4798,7 +5636,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="23" spans="2:52" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:52" x14ac:dyDescent="0.4">
       <c r="B23" s="7" t="s">
         <v>57</v>
       </c>
@@ -4809,7 +5647,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="24" spans="2:52" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:52" x14ac:dyDescent="0.4">
       <c r="B24" s="7" t="s">
         <v>58</v>
       </c>
@@ -4820,7 +5658,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="25" spans="2:52" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:52" x14ac:dyDescent="0.4">
       <c r="B25" s="7" t="s">
         <v>59</v>
       </c>
@@ -4831,7 +5669,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="26" spans="2:52" s="5" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:52" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="B26" s="8" t="s">
         <v>60</v>
       </c>
@@ -4842,7 +5680,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="27" spans="2:52" s="5" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:52" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="B27" s="12" t="s">
         <v>61</v>
       </c>
@@ -4853,7 +5691,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="28" spans="2:52" s="5" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:52" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="B28" s="8" t="s">
         <v>62</v>
       </c>
@@ -4864,23 +5702,2983 @@
         <v>567</v>
       </c>
     </row>
-    <row r="29" spans="2:52" s="5" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:52" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="B29" t="s">
         <v>39</v>
       </c>
       <c r="C29" s="6"/>
     </row>
-    <row r="30" spans="2:52" s="5" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:52" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="B30" t="s">
         <v>25</v>
       </c>
       <c r="C30" s="6"/>
     </row>
-    <row r="31" spans="2:52" s="5" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="2:52" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
     </row>
-    <row r="32" spans="2:52" s="5" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="2:52" s="5" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="B32" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C32" s="6"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" verticalDpi="0" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65309343-5134-42B2-91CD-0F008F8E70CA}">
+  <dimension ref="B1:BK32"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="2" max="2" width="32" bestFit="1" customWidth="1"/>
+    <col min="3" max="52" width="9.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:63" x14ac:dyDescent="0.4">
+      <c r="B1" s="23" t="s">
+        <v>570</v>
+      </c>
+      <c r="C1" t="s">
+        <v>568</v>
+      </c>
+      <c r="D1" t="s">
+        <v>569</v>
+      </c>
+      <c r="E1" t="s">
+        <v>571</v>
+      </c>
+      <c r="F1" t="s">
+        <v>572</v>
+      </c>
+      <c r="G1" t="s">
+        <v>573</v>
+      </c>
+      <c r="H1" t="s">
+        <v>574</v>
+      </c>
+      <c r="I1" t="s">
+        <v>575</v>
+      </c>
+      <c r="J1" t="s">
+        <v>576</v>
+      </c>
+      <c r="K1" t="s">
+        <v>577</v>
+      </c>
+      <c r="L1" t="s">
+        <v>578</v>
+      </c>
+      <c r="M1" t="s">
+        <v>579</v>
+      </c>
+      <c r="N1" t="s">
+        <v>580</v>
+      </c>
+      <c r="O1" t="s">
+        <v>581</v>
+      </c>
+      <c r="P1" t="s">
+        <v>582</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>583</v>
+      </c>
+      <c r="R1" t="s">
+        <v>584</v>
+      </c>
+      <c r="S1" t="s">
+        <v>585</v>
+      </c>
+      <c r="T1" t="s">
+        <v>586</v>
+      </c>
+      <c r="U1" t="s">
+        <v>587</v>
+      </c>
+      <c r="V1" t="s">
+        <v>588</v>
+      </c>
+      <c r="W1" t="s">
+        <v>589</v>
+      </c>
+      <c r="X1" t="s">
+        <v>590</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>591</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>592</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>593</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>594</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>595</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>596</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>597</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>598</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>599</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>600</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>601</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>602</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>603</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>604</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>605</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>606</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>607</v>
+      </c>
+      <c r="AP1" t="s">
+        <v>608</v>
+      </c>
+      <c r="AQ1" t="s">
+        <v>609</v>
+      </c>
+      <c r="AR1" t="s">
+        <v>610</v>
+      </c>
+      <c r="AS1" t="s">
+        <v>611</v>
+      </c>
+      <c r="AT1" t="s">
+        <v>612</v>
+      </c>
+      <c r="AU1" t="s">
+        <v>613</v>
+      </c>
+      <c r="AV1" t="s">
+        <v>614</v>
+      </c>
+      <c r="AW1" t="s">
+        <v>615</v>
+      </c>
+      <c r="AX1" t="s">
+        <v>616</v>
+      </c>
+      <c r="AY1" t="s">
+        <v>617</v>
+      </c>
+      <c r="AZ1" t="s">
+        <v>618</v>
+      </c>
+      <c r="BA1" t="s">
+        <v>641</v>
+      </c>
+      <c r="BB1" t="s">
+        <v>642</v>
+      </c>
+      <c r="BC1" t="s">
+        <v>643</v>
+      </c>
+      <c r="BD1" t="s">
+        <v>644</v>
+      </c>
+      <c r="BE1" t="s">
+        <v>645</v>
+      </c>
+      <c r="BF1" t="s">
+        <v>646</v>
+      </c>
+      <c r="BG1" t="s">
+        <v>647</v>
+      </c>
+      <c r="BH1" t="s">
+        <v>648</v>
+      </c>
+      <c r="BI1" t="s">
+        <v>649</v>
+      </c>
+      <c r="BJ1" t="s">
+        <v>650</v>
+      </c>
+      <c r="BK1" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="2" spans="2:63" x14ac:dyDescent="0.4">
+      <c r="B2" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H2" t="s">
+        <v>72</v>
+      </c>
+      <c r="I2" t="s">
+        <v>73</v>
+      </c>
+      <c r="J2" t="s">
+        <v>76</v>
+      </c>
+      <c r="K2" t="s">
+        <v>77</v>
+      </c>
+      <c r="L2" t="s">
+        <v>78</v>
+      </c>
+      <c r="M2" t="s">
+        <v>79</v>
+      </c>
+      <c r="N2" t="s">
+        <v>80</v>
+      </c>
+      <c r="O2" t="s">
+        <v>81</v>
+      </c>
+      <c r="P2" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>83</v>
+      </c>
+      <c r="R2" t="s">
+        <v>84</v>
+      </c>
+      <c r="S2" t="s">
+        <v>85</v>
+      </c>
+      <c r="T2" t="s">
+        <v>86</v>
+      </c>
+      <c r="U2" t="s">
+        <v>87</v>
+      </c>
+      <c r="V2" t="s">
+        <v>88</v>
+      </c>
+      <c r="W2" t="s">
+        <v>89</v>
+      </c>
+      <c r="X2" t="s">
+        <v>90</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>91</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>92</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>93</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>94</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>95</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>96</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>97</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>99</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>100</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>103</v>
+      </c>
+      <c r="AL2" t="s">
+        <v>104</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>105</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>106</v>
+      </c>
+      <c r="AO2" t="s">
+        <v>107</v>
+      </c>
+      <c r="AP2" t="s">
+        <v>108</v>
+      </c>
+      <c r="AQ2" t="s">
+        <v>109</v>
+      </c>
+      <c r="AR2" t="s">
+        <v>215</v>
+      </c>
+      <c r="AS2" t="s">
+        <v>216</v>
+      </c>
+      <c r="AT2" t="s">
+        <v>217</v>
+      </c>
+      <c r="AU2" t="s">
+        <v>218</v>
+      </c>
+      <c r="AV2" t="s">
+        <v>219</v>
+      </c>
+      <c r="AW2" t="s">
+        <v>220</v>
+      </c>
+      <c r="AX2" t="s">
+        <v>221</v>
+      </c>
+      <c r="AY2" t="s">
+        <v>222</v>
+      </c>
+      <c r="AZ2" t="s">
+        <v>247</v>
+      </c>
+      <c r="BA2" t="s">
+        <v>630</v>
+      </c>
+      <c r="BB2" t="s">
+        <v>631</v>
+      </c>
+      <c r="BC2" t="s">
+        <v>632</v>
+      </c>
+      <c r="BD2" t="s">
+        <v>633</v>
+      </c>
+      <c r="BE2" t="s">
+        <v>634</v>
+      </c>
+      <c r="BF2" t="s">
+        <v>635</v>
+      </c>
+      <c r="BG2" t="s">
+        <v>636</v>
+      </c>
+      <c r="BH2" t="s">
+        <v>637</v>
+      </c>
+      <c r="BI2" t="s">
+        <v>638</v>
+      </c>
+      <c r="BJ2" t="s">
+        <v>639</v>
+      </c>
+      <c r="BK2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="3" spans="2:63" x14ac:dyDescent="0.4">
+      <c r="B3" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C3" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="D3" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="E3" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="F3" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="G3" s="22" t="s">
+        <v>524</v>
+      </c>
+      <c r="H3" s="22" t="s">
+        <v>525</v>
+      </c>
+      <c r="I3" s="22" t="s">
+        <v>526</v>
+      </c>
+      <c r="J3" s="22" t="s">
+        <v>527</v>
+      </c>
+      <c r="K3" s="22" t="s">
+        <v>528</v>
+      </c>
+      <c r="L3" s="22" t="s">
+        <v>529</v>
+      </c>
+      <c r="M3" s="22" t="s">
+        <v>530</v>
+      </c>
+      <c r="N3" s="22" t="s">
+        <v>531</v>
+      </c>
+      <c r="O3" s="22" t="s">
+        <v>532</v>
+      </c>
+      <c r="P3" s="21" t="s">
+        <v>561</v>
+      </c>
+      <c r="Q3" s="21" t="s">
+        <v>561</v>
+      </c>
+      <c r="R3" s="21" t="s">
+        <v>561</v>
+      </c>
+      <c r="S3" s="21" t="s">
+        <v>561</v>
+      </c>
+      <c r="T3" s="21" t="s">
+        <v>561</v>
+      </c>
+      <c r="U3" s="13" t="s">
+        <v>561</v>
+      </c>
+      <c r="V3" s="13" t="s">
+        <v>561</v>
+      </c>
+      <c r="W3" s="21" t="s">
+        <v>538</v>
+      </c>
+      <c r="X3" s="10" t="s">
+        <v>539</v>
+      </c>
+      <c r="Y3" s="21" t="s">
+        <v>627</v>
+      </c>
+      <c r="Z3" s="10" t="s">
+        <v>541</v>
+      </c>
+      <c r="AA3" s="22" t="s">
+        <v>542</v>
+      </c>
+      <c r="AB3" s="22" t="s">
+        <v>543</v>
+      </c>
+      <c r="AC3" s="21" t="s">
+        <v>561</v>
+      </c>
+      <c r="AD3" s="21" t="s">
+        <v>625</v>
+      </c>
+      <c r="AE3" s="21" t="s">
+        <v>561</v>
+      </c>
+      <c r="AF3" s="21" t="s">
+        <v>629</v>
+      </c>
+      <c r="AG3" s="21" t="s">
+        <v>628</v>
+      </c>
+      <c r="AH3" s="22" t="s">
+        <v>549</v>
+      </c>
+      <c r="AI3" s="22" t="s">
+        <v>550</v>
+      </c>
+      <c r="AJ3" s="21" t="s">
+        <v>561</v>
+      </c>
+      <c r="AK3" s="22" t="s">
+        <v>551</v>
+      </c>
+      <c r="AL3" s="22" t="s">
+        <v>620</v>
+      </c>
+      <c r="AM3" s="21" t="s">
+        <v>619</v>
+      </c>
+      <c r="AN3" s="22" t="s">
+        <v>621</v>
+      </c>
+      <c r="AO3" s="22" t="s">
+        <v>622</v>
+      </c>
+      <c r="AP3" s="22" t="s">
+        <v>623</v>
+      </c>
+      <c r="AQ3" s="22" t="s">
+        <v>624</v>
+      </c>
+      <c r="AR3" s="22" t="s">
+        <v>559</v>
+      </c>
+      <c r="AS3" s="22" t="s">
+        <v>560</v>
+      </c>
+      <c r="AT3" s="21" t="s">
+        <v>626</v>
+      </c>
+      <c r="AU3" s="13" t="s">
+        <v>561</v>
+      </c>
+      <c r="AV3" s="13" t="s">
+        <v>561</v>
+      </c>
+      <c r="AW3" s="13" t="s">
+        <v>561</v>
+      </c>
+      <c r="AX3" s="13" t="s">
+        <v>561</v>
+      </c>
+      <c r="AY3" s="13" t="s">
+        <v>561</v>
+      </c>
+      <c r="AZ3" s="21" t="s">
+        <v>653</v>
+      </c>
+      <c r="BA3" s="13" t="s">
+        <v>561</v>
+      </c>
+      <c r="BB3" s="13" t="s">
+        <v>561</v>
+      </c>
+      <c r="BC3" s="13" t="s">
+        <v>561</v>
+      </c>
+      <c r="BD3" s="21" t="s">
+        <v>652</v>
+      </c>
+      <c r="BE3" s="13" t="s">
+        <v>561</v>
+      </c>
+      <c r="BF3" s="13" t="s">
+        <v>561</v>
+      </c>
+      <c r="BG3" s="13" t="s">
+        <v>561</v>
+      </c>
+      <c r="BH3" s="13" t="s">
+        <v>561</v>
+      </c>
+      <c r="BI3" s="13" t="s">
+        <v>561</v>
+      </c>
+      <c r="BJ3" s="13" t="s">
+        <v>561</v>
+      </c>
+      <c r="BK3" s="13" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="4" spans="2:63" x14ac:dyDescent="0.4">
+      <c r="B4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" t="s">
+        <v>34</v>
+      </c>
+      <c r="F4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G4" t="s">
+        <v>36</v>
+      </c>
+      <c r="H4" t="s">
+        <v>37</v>
+      </c>
+      <c r="I4" t="s">
+        <v>110</v>
+      </c>
+      <c r="J4" t="s">
+        <v>113</v>
+      </c>
+      <c r="K4" t="s">
+        <v>116</v>
+      </c>
+      <c r="L4" t="s">
+        <v>117</v>
+      </c>
+      <c r="M4" t="s">
+        <v>118</v>
+      </c>
+      <c r="N4" t="s">
+        <v>119</v>
+      </c>
+      <c r="O4" t="s">
+        <v>120</v>
+      </c>
+      <c r="P4" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>122</v>
+      </c>
+      <c r="R4" t="s">
+        <v>123</v>
+      </c>
+      <c r="S4" t="s">
+        <v>124</v>
+      </c>
+      <c r="T4" t="s">
+        <v>125</v>
+      </c>
+      <c r="U4" t="s">
+        <v>126</v>
+      </c>
+      <c r="V4" t="s">
+        <v>127</v>
+      </c>
+      <c r="W4" t="s">
+        <v>128</v>
+      </c>
+      <c r="X4" t="s">
+        <v>129</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>130</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>131</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>132</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>133</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>134</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>135</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>136</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>137</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>138</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>139</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>140</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>141</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>142</v>
+      </c>
+      <c r="AL4" t="s">
+        <v>143</v>
+      </c>
+      <c r="AM4" t="s">
+        <v>144</v>
+      </c>
+      <c r="AN4" t="s">
+        <v>145</v>
+      </c>
+      <c r="AO4" t="s">
+        <v>146</v>
+      </c>
+      <c r="AP4" t="s">
+        <v>147</v>
+      </c>
+      <c r="AQ4" t="s">
+        <v>148</v>
+      </c>
+      <c r="AR4" t="s">
+        <v>223</v>
+      </c>
+      <c r="AS4" t="s">
+        <v>224</v>
+      </c>
+      <c r="AT4" t="s">
+        <v>225</v>
+      </c>
+      <c r="AU4" t="s">
+        <v>226</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>227</v>
+      </c>
+      <c r="AW4" t="s">
+        <v>228</v>
+      </c>
+      <c r="AX4" t="s">
+        <v>229</v>
+      </c>
+      <c r="AY4" t="s">
+        <v>230</v>
+      </c>
+      <c r="AZ4" t="s">
+        <v>21</v>
+      </c>
+      <c r="BA4" t="s">
+        <v>720</v>
+      </c>
+      <c r="BB4" t="s">
+        <v>721</v>
+      </c>
+      <c r="BC4" t="s">
+        <v>722</v>
+      </c>
+      <c r="BD4" t="s">
+        <v>723</v>
+      </c>
+      <c r="BE4" t="s">
+        <v>724</v>
+      </c>
+      <c r="BF4" t="s">
+        <v>725</v>
+      </c>
+      <c r="BG4" t="s">
+        <v>726</v>
+      </c>
+      <c r="BH4" t="s">
+        <v>727</v>
+      </c>
+      <c r="BI4" t="s">
+        <v>728</v>
+      </c>
+      <c r="BJ4" t="s">
+        <v>729</v>
+      </c>
+      <c r="BK4" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="5" spans="2:63" x14ac:dyDescent="0.4">
+      <c r="B5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" t="s">
+        <v>111</v>
+      </c>
+      <c r="J5" t="s">
+        <v>114</v>
+      </c>
+      <c r="K5" t="s">
+        <v>149</v>
+      </c>
+      <c r="L5" t="s">
+        <v>150</v>
+      </c>
+      <c r="M5" t="s">
+        <v>151</v>
+      </c>
+      <c r="N5" t="s">
+        <v>152</v>
+      </c>
+      <c r="O5" t="s">
+        <v>153</v>
+      </c>
+      <c r="P5" t="s">
+        <v>154</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>155</v>
+      </c>
+      <c r="R5" t="s">
+        <v>156</v>
+      </c>
+      <c r="S5" t="s">
+        <v>157</v>
+      </c>
+      <c r="T5" t="s">
+        <v>158</v>
+      </c>
+      <c r="U5" t="s">
+        <v>159</v>
+      </c>
+      <c r="V5" t="s">
+        <v>160</v>
+      </c>
+      <c r="W5" t="s">
+        <v>161</v>
+      </c>
+      <c r="X5" t="s">
+        <v>162</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>163</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>164</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>165</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>166</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>167</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>168</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>169</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>170</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>171</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>172</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>173</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>174</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>175</v>
+      </c>
+      <c r="AL5" t="s">
+        <v>176</v>
+      </c>
+      <c r="AM5" t="s">
+        <v>177</v>
+      </c>
+      <c r="AN5" t="s">
+        <v>178</v>
+      </c>
+      <c r="AO5" t="s">
+        <v>179</v>
+      </c>
+      <c r="AP5" t="s">
+        <v>180</v>
+      </c>
+      <c r="AQ5" t="s">
+        <v>181</v>
+      </c>
+      <c r="AR5" t="s">
+        <v>231</v>
+      </c>
+      <c r="AS5" t="s">
+        <v>232</v>
+      </c>
+      <c r="AT5" t="s">
+        <v>233</v>
+      </c>
+      <c r="AU5" t="s">
+        <v>234</v>
+      </c>
+      <c r="AV5" t="s">
+        <v>235</v>
+      </c>
+      <c r="AW5" t="s">
+        <v>236</v>
+      </c>
+      <c r="AX5" t="s">
+        <v>237</v>
+      </c>
+      <c r="AY5" t="s">
+        <v>238</v>
+      </c>
+      <c r="AZ5" t="s">
+        <v>22</v>
+      </c>
+      <c r="BA5" t="s">
+        <v>731</v>
+      </c>
+      <c r="BB5" t="s">
+        <v>732</v>
+      </c>
+      <c r="BC5" t="s">
+        <v>733</v>
+      </c>
+      <c r="BD5" t="s">
+        <v>734</v>
+      </c>
+      <c r="BE5" t="s">
+        <v>735</v>
+      </c>
+      <c r="BF5" t="s">
+        <v>736</v>
+      </c>
+      <c r="BG5" t="s">
+        <v>737</v>
+      </c>
+      <c r="BH5" t="s">
+        <v>738</v>
+      </c>
+      <c r="BI5" t="s">
+        <v>739</v>
+      </c>
+      <c r="BJ5" t="s">
+        <v>740</v>
+      </c>
+      <c r="BK5" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="6" spans="2:63" x14ac:dyDescent="0.4">
+      <c r="B6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" t="s">
+        <v>29</v>
+      </c>
+      <c r="G6" t="s">
+        <v>30</v>
+      </c>
+      <c r="H6" t="s">
+        <v>31</v>
+      </c>
+      <c r="I6" t="s">
+        <v>112</v>
+      </c>
+      <c r="J6" t="s">
+        <v>115</v>
+      </c>
+      <c r="K6" t="s">
+        <v>182</v>
+      </c>
+      <c r="L6" t="s">
+        <v>183</v>
+      </c>
+      <c r="M6" t="s">
+        <v>184</v>
+      </c>
+      <c r="N6" t="s">
+        <v>185</v>
+      </c>
+      <c r="O6" t="s">
+        <v>186</v>
+      </c>
+      <c r="P6" t="s">
+        <v>187</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>188</v>
+      </c>
+      <c r="R6" t="s">
+        <v>189</v>
+      </c>
+      <c r="S6" t="s">
+        <v>190</v>
+      </c>
+      <c r="T6" t="s">
+        <v>191</v>
+      </c>
+      <c r="U6" t="s">
+        <v>192</v>
+      </c>
+      <c r="V6" t="s">
+        <v>193</v>
+      </c>
+      <c r="W6" t="s">
+        <v>194</v>
+      </c>
+      <c r="X6" t="s">
+        <v>195</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>196</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>197</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>198</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>199</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>200</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>201</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>202</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>203</v>
+      </c>
+      <c r="AG6" t="s">
+        <v>204</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>205</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>206</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AK6" t="s">
+        <v>208</v>
+      </c>
+      <c r="AL6" t="s">
+        <v>209</v>
+      </c>
+      <c r="AM6" t="s">
+        <v>210</v>
+      </c>
+      <c r="AN6" t="s">
+        <v>211</v>
+      </c>
+      <c r="AO6" t="s">
+        <v>212</v>
+      </c>
+      <c r="AP6" t="s">
+        <v>213</v>
+      </c>
+      <c r="AQ6" t="s">
+        <v>214</v>
+      </c>
+      <c r="AR6" t="s">
+        <v>239</v>
+      </c>
+      <c r="AS6" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT6" t="s">
+        <v>241</v>
+      </c>
+      <c r="AU6" t="s">
+        <v>242</v>
+      </c>
+      <c r="AV6" t="s">
+        <v>243</v>
+      </c>
+      <c r="AW6" t="s">
+        <v>244</v>
+      </c>
+      <c r="AX6" t="s">
+        <v>245</v>
+      </c>
+      <c r="AY6" t="s">
+        <v>246</v>
+      </c>
+      <c r="AZ6" t="s">
+        <v>32</v>
+      </c>
+      <c r="BA6" t="s">
+        <v>742</v>
+      </c>
+      <c r="BB6" t="s">
+        <v>743</v>
+      </c>
+      <c r="BC6" t="s">
+        <v>744</v>
+      </c>
+      <c r="BD6" t="s">
+        <v>745</v>
+      </c>
+      <c r="BE6" t="s">
+        <v>746</v>
+      </c>
+      <c r="BF6" t="s">
+        <v>747</v>
+      </c>
+      <c r="BG6" t="s">
+        <v>748</v>
+      </c>
+      <c r="BH6" t="s">
+        <v>749</v>
+      </c>
+      <c r="BI6" t="s">
+        <v>750</v>
+      </c>
+      <c r="BJ6" t="s">
+        <v>751</v>
+      </c>
+      <c r="BK6" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="8" spans="2:63" x14ac:dyDescent="0.4">
+      <c r="B8" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="9" spans="2:63" x14ac:dyDescent="0.4">
+      <c r="B9" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" t="s">
+        <v>40</v>
+      </c>
+      <c r="D9" t="s">
+        <v>44</v>
+      </c>
+      <c r="E9" t="s">
+        <v>41</v>
+      </c>
+      <c r="F9" t="s">
+        <v>42</v>
+      </c>
+      <c r="G9" t="s">
+        <v>45</v>
+      </c>
+      <c r="H9" t="s">
+        <v>46</v>
+      </c>
+      <c r="I9" t="s">
+        <v>248</v>
+      </c>
+      <c r="J9" t="s">
+        <v>249</v>
+      </c>
+      <c r="K9" t="s">
+        <v>250</v>
+      </c>
+      <c r="L9" t="s">
+        <v>251</v>
+      </c>
+      <c r="M9" t="s">
+        <v>252</v>
+      </c>
+      <c r="N9" t="s">
+        <v>253</v>
+      </c>
+      <c r="O9" t="s">
+        <v>254</v>
+      </c>
+      <c r="P9" t="s">
+        <v>255</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>256</v>
+      </c>
+      <c r="R9" t="s">
+        <v>257</v>
+      </c>
+      <c r="S9" t="s">
+        <v>258</v>
+      </c>
+      <c r="T9" t="s">
+        <v>259</v>
+      </c>
+      <c r="U9" t="s">
+        <v>260</v>
+      </c>
+      <c r="V9" t="s">
+        <v>261</v>
+      </c>
+      <c r="W9" t="s">
+        <v>262</v>
+      </c>
+      <c r="X9" t="s">
+        <v>263</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>264</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>265</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>266</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>267</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>268</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>269</v>
+      </c>
+      <c r="AE9" t="s">
+        <v>270</v>
+      </c>
+      <c r="AF9" t="s">
+        <v>271</v>
+      </c>
+      <c r="AG9" t="s">
+        <v>272</v>
+      </c>
+      <c r="AH9" t="s">
+        <v>273</v>
+      </c>
+      <c r="AI9" t="s">
+        <v>274</v>
+      </c>
+      <c r="AJ9" t="s">
+        <v>275</v>
+      </c>
+      <c r="AK9" t="s">
+        <v>276</v>
+      </c>
+      <c r="AL9" t="s">
+        <v>277</v>
+      </c>
+      <c r="AM9" t="s">
+        <v>278</v>
+      </c>
+      <c r="AN9" t="s">
+        <v>279</v>
+      </c>
+      <c r="AO9" t="s">
+        <v>280</v>
+      </c>
+      <c r="AP9" t="s">
+        <v>281</v>
+      </c>
+      <c r="AQ9" t="s">
+        <v>282</v>
+      </c>
+      <c r="AR9" t="s">
+        <v>283</v>
+      </c>
+      <c r="AS9" t="s">
+        <v>284</v>
+      </c>
+      <c r="AT9" t="s">
+        <v>285</v>
+      </c>
+      <c r="AU9" t="s">
+        <v>286</v>
+      </c>
+      <c r="AV9" t="s">
+        <v>287</v>
+      </c>
+      <c r="AW9" t="s">
+        <v>288</v>
+      </c>
+      <c r="AX9" t="s">
+        <v>289</v>
+      </c>
+      <c r="AY9" t="s">
+        <v>290</v>
+      </c>
+      <c r="AZ9" t="s">
+        <v>291</v>
+      </c>
+      <c r="BA9" t="s">
+        <v>654</v>
+      </c>
+      <c r="BB9" t="s">
+        <v>655</v>
+      </c>
+      <c r="BC9" t="s">
+        <v>656</v>
+      </c>
+      <c r="BD9" t="s">
+        <v>657</v>
+      </c>
+      <c r="BE9" t="s">
+        <v>658</v>
+      </c>
+      <c r="BF9" t="s">
+        <v>659</v>
+      </c>
+      <c r="BG9" t="s">
+        <v>660</v>
+      </c>
+      <c r="BH9" t="s">
+        <v>661</v>
+      </c>
+      <c r="BI9" t="s">
+        <v>662</v>
+      </c>
+      <c r="BJ9" t="s">
+        <v>663</v>
+      </c>
+      <c r="BK9" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="10" spans="2:63" x14ac:dyDescent="0.4">
+      <c r="B10" s="1"/>
+      <c r="C10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" t="s">
+        <v>3</v>
+      </c>
+      <c r="E10" t="s">
+        <v>3</v>
+      </c>
+      <c r="F10" t="s">
+        <v>3</v>
+      </c>
+      <c r="G10" t="s">
+        <v>3</v>
+      </c>
+      <c r="H10" t="s">
+        <v>3</v>
+      </c>
+      <c r="I10" t="s">
+        <v>3</v>
+      </c>
+      <c r="J10" t="s">
+        <v>3</v>
+      </c>
+      <c r="K10" t="s">
+        <v>3</v>
+      </c>
+      <c r="L10" t="s">
+        <v>3</v>
+      </c>
+      <c r="M10" t="s">
+        <v>3</v>
+      </c>
+      <c r="N10" t="s">
+        <v>3</v>
+      </c>
+      <c r="O10" t="s">
+        <v>3</v>
+      </c>
+      <c r="P10" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>3</v>
+      </c>
+      <c r="R10" t="s">
+        <v>3</v>
+      </c>
+      <c r="S10" t="s">
+        <v>3</v>
+      </c>
+      <c r="T10" t="s">
+        <v>3</v>
+      </c>
+      <c r="U10" t="s">
+        <v>3</v>
+      </c>
+      <c r="V10" t="s">
+        <v>3</v>
+      </c>
+      <c r="W10" t="s">
+        <v>3</v>
+      </c>
+      <c r="X10" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE10" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF10" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG10" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH10" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI10" t="s">
+        <v>3</v>
+      </c>
+      <c r="AJ10" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK10" t="s">
+        <v>3</v>
+      </c>
+      <c r="AL10" t="s">
+        <v>3</v>
+      </c>
+      <c r="AM10" t="s">
+        <v>3</v>
+      </c>
+      <c r="AN10" t="s">
+        <v>3</v>
+      </c>
+      <c r="AO10" t="s">
+        <v>3</v>
+      </c>
+      <c r="AP10" t="s">
+        <v>3</v>
+      </c>
+      <c r="AQ10" t="s">
+        <v>3</v>
+      </c>
+      <c r="AR10" t="s">
+        <v>3</v>
+      </c>
+      <c r="AS10" t="s">
+        <v>3</v>
+      </c>
+      <c r="AT10" t="s">
+        <v>3</v>
+      </c>
+      <c r="AU10" t="s">
+        <v>3</v>
+      </c>
+      <c r="AV10" t="s">
+        <v>3</v>
+      </c>
+      <c r="AW10" t="s">
+        <v>3</v>
+      </c>
+      <c r="AX10" t="s">
+        <v>3</v>
+      </c>
+      <c r="AY10" t="s">
+        <v>3</v>
+      </c>
+      <c r="AZ10" t="s">
+        <v>3</v>
+      </c>
+      <c r="BA10" t="s">
+        <v>3</v>
+      </c>
+      <c r="BB10" t="s">
+        <v>3</v>
+      </c>
+      <c r="BC10" t="s">
+        <v>3</v>
+      </c>
+      <c r="BD10" t="s">
+        <v>3</v>
+      </c>
+      <c r="BE10" t="s">
+        <v>3</v>
+      </c>
+      <c r="BF10" t="s">
+        <v>3</v>
+      </c>
+      <c r="BG10" t="s">
+        <v>3</v>
+      </c>
+      <c r="BH10" t="s">
+        <v>3</v>
+      </c>
+      <c r="BI10" t="s">
+        <v>3</v>
+      </c>
+      <c r="BJ10" t="s">
+        <v>3</v>
+      </c>
+      <c r="BK10" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="2:63" x14ac:dyDescent="0.4">
+      <c r="B11" s="2"/>
+      <c r="C11" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" t="s">
+        <v>47</v>
+      </c>
+      <c r="E11" t="s">
+        <v>48</v>
+      </c>
+      <c r="F11" t="s">
+        <v>49</v>
+      </c>
+      <c r="G11" t="s">
+        <v>50</v>
+      </c>
+      <c r="H11" t="s">
+        <v>51</v>
+      </c>
+      <c r="I11" t="s">
+        <v>292</v>
+      </c>
+      <c r="J11" t="s">
+        <v>293</v>
+      </c>
+      <c r="K11" t="s">
+        <v>294</v>
+      </c>
+      <c r="L11" t="s">
+        <v>295</v>
+      </c>
+      <c r="M11" t="s">
+        <v>296</v>
+      </c>
+      <c r="N11" t="s">
+        <v>297</v>
+      </c>
+      <c r="O11" t="s">
+        <v>298</v>
+      </c>
+      <c r="P11" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>300</v>
+      </c>
+      <c r="R11" t="s">
+        <v>301</v>
+      </c>
+      <c r="S11" t="s">
+        <v>302</v>
+      </c>
+      <c r="T11" t="s">
+        <v>303</v>
+      </c>
+      <c r="U11" t="s">
+        <v>304</v>
+      </c>
+      <c r="V11" t="s">
+        <v>305</v>
+      </c>
+      <c r="W11" t="s">
+        <v>306</v>
+      </c>
+      <c r="X11" t="s">
+        <v>307</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>308</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>309</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>310</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>311</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>312</v>
+      </c>
+      <c r="AD11" t="s">
+        <v>313</v>
+      </c>
+      <c r="AE11" t="s">
+        <v>314</v>
+      </c>
+      <c r="AF11" t="s">
+        <v>315</v>
+      </c>
+      <c r="AG11" t="s">
+        <v>316</v>
+      </c>
+      <c r="AH11" t="s">
+        <v>317</v>
+      </c>
+      <c r="AI11" t="s">
+        <v>318</v>
+      </c>
+      <c r="AJ11" t="s">
+        <v>319</v>
+      </c>
+      <c r="AK11" t="s">
+        <v>320</v>
+      </c>
+      <c r="AL11" t="s">
+        <v>321</v>
+      </c>
+      <c r="AM11" t="s">
+        <v>322</v>
+      </c>
+      <c r="AN11" t="s">
+        <v>323</v>
+      </c>
+      <c r="AO11" t="s">
+        <v>324</v>
+      </c>
+      <c r="AP11" t="s">
+        <v>325</v>
+      </c>
+      <c r="AQ11" t="s">
+        <v>326</v>
+      </c>
+      <c r="AR11" t="s">
+        <v>327</v>
+      </c>
+      <c r="AS11" t="s">
+        <v>328</v>
+      </c>
+      <c r="AT11" t="s">
+        <v>329</v>
+      </c>
+      <c r="AU11" t="s">
+        <v>330</v>
+      </c>
+      <c r="AV11" t="s">
+        <v>331</v>
+      </c>
+      <c r="AW11" t="s">
+        <v>332</v>
+      </c>
+      <c r="AX11" t="s">
+        <v>333</v>
+      </c>
+      <c r="AY11" t="s">
+        <v>334</v>
+      </c>
+      <c r="AZ11" t="s">
+        <v>335</v>
+      </c>
+      <c r="BA11" t="s">
+        <v>665</v>
+      </c>
+      <c r="BB11" t="s">
+        <v>666</v>
+      </c>
+      <c r="BC11" t="s">
+        <v>667</v>
+      </c>
+      <c r="BD11" t="s">
+        <v>668</v>
+      </c>
+      <c r="BE11" t="s">
+        <v>669</v>
+      </c>
+      <c r="BF11" t="s">
+        <v>670</v>
+      </c>
+      <c r="BG11" t="s">
+        <v>671</v>
+      </c>
+      <c r="BH11" t="s">
+        <v>672</v>
+      </c>
+      <c r="BI11" t="s">
+        <v>673</v>
+      </c>
+      <c r="BJ11" t="s">
+        <v>674</v>
+      </c>
+      <c r="BK11" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="12" spans="2:63" x14ac:dyDescent="0.4">
+      <c r="B12" s="2"/>
+    </row>
+    <row r="13" spans="2:63" x14ac:dyDescent="0.4">
+      <c r="B13" s="2">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="C13" t="s">
+        <v>2</v>
+      </c>
+      <c r="D13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E13" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" t="s">
+        <v>14</v>
+      </c>
+      <c r="G13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H13" t="s">
+        <v>16</v>
+      </c>
+      <c r="I13" t="s">
+        <v>336</v>
+      </c>
+      <c r="J13" t="s">
+        <v>337</v>
+      </c>
+      <c r="K13" t="s">
+        <v>338</v>
+      </c>
+      <c r="L13" t="s">
+        <v>339</v>
+      </c>
+      <c r="M13" t="s">
+        <v>340</v>
+      </c>
+      <c r="N13" t="s">
+        <v>341</v>
+      </c>
+      <c r="O13" t="s">
+        <v>342</v>
+      </c>
+      <c r="P13" t="s">
+        <v>343</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>344</v>
+      </c>
+      <c r="R13" t="s">
+        <v>345</v>
+      </c>
+      <c r="S13" t="s">
+        <v>346</v>
+      </c>
+      <c r="T13" t="s">
+        <v>347</v>
+      </c>
+      <c r="U13" t="s">
+        <v>348</v>
+      </c>
+      <c r="V13" t="s">
+        <v>349</v>
+      </c>
+      <c r="W13" t="s">
+        <v>350</v>
+      </c>
+      <c r="X13" t="s">
+        <v>351</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>352</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>353</v>
+      </c>
+      <c r="AA13" t="s">
+        <v>354</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>355</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>356</v>
+      </c>
+      <c r="AD13" t="s">
+        <v>357</v>
+      </c>
+      <c r="AE13" t="s">
+        <v>358</v>
+      </c>
+      <c r="AF13" t="s">
+        <v>359</v>
+      </c>
+      <c r="AG13" t="s">
+        <v>360</v>
+      </c>
+      <c r="AH13" t="s">
+        <v>361</v>
+      </c>
+      <c r="AI13" t="s">
+        <v>362</v>
+      </c>
+      <c r="AJ13" t="s">
+        <v>363</v>
+      </c>
+      <c r="AK13" t="s">
+        <v>364</v>
+      </c>
+      <c r="AL13" t="s">
+        <v>365</v>
+      </c>
+      <c r="AM13" t="s">
+        <v>366</v>
+      </c>
+      <c r="AN13" t="s">
+        <v>367</v>
+      </c>
+      <c r="AO13" t="s">
+        <v>368</v>
+      </c>
+      <c r="AP13" t="s">
+        <v>369</v>
+      </c>
+      <c r="AQ13" t="s">
+        <v>370</v>
+      </c>
+      <c r="AR13" t="s">
+        <v>371</v>
+      </c>
+      <c r="AS13" t="s">
+        <v>372</v>
+      </c>
+      <c r="AT13" t="s">
+        <v>373</v>
+      </c>
+      <c r="AU13" t="s">
+        <v>374</v>
+      </c>
+      <c r="AV13" t="s">
+        <v>375</v>
+      </c>
+      <c r="AW13" t="s">
+        <v>376</v>
+      </c>
+      <c r="AX13" t="s">
+        <v>377</v>
+      </c>
+      <c r="AY13" t="s">
+        <v>378</v>
+      </c>
+      <c r="AZ13" t="s">
+        <v>379</v>
+      </c>
+      <c r="BA13" t="s">
+        <v>676</v>
+      </c>
+      <c r="BB13" t="s">
+        <v>677</v>
+      </c>
+      <c r="BC13" t="s">
+        <v>678</v>
+      </c>
+      <c r="BD13" t="s">
+        <v>679</v>
+      </c>
+      <c r="BE13" t="s">
+        <v>680</v>
+      </c>
+      <c r="BF13" t="s">
+        <v>681</v>
+      </c>
+      <c r="BG13" t="s">
+        <v>682</v>
+      </c>
+      <c r="BH13" t="s">
+        <v>683</v>
+      </c>
+      <c r="BI13" t="s">
+        <v>684</v>
+      </c>
+      <c r="BJ13" t="s">
+        <v>685</v>
+      </c>
+      <c r="BK13" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="14" spans="2:63" x14ac:dyDescent="0.4">
+      <c r="B14" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C14" t="s">
+        <v>3</v>
+      </c>
+      <c r="D14" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" t="s">
+        <v>3</v>
+      </c>
+      <c r="K14" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" t="s">
+        <v>3</v>
+      </c>
+      <c r="O14" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>3</v>
+      </c>
+      <c r="R14" t="s">
+        <v>3</v>
+      </c>
+      <c r="S14" t="s">
+        <v>3</v>
+      </c>
+      <c r="T14" t="s">
+        <v>3</v>
+      </c>
+      <c r="U14" t="s">
+        <v>3</v>
+      </c>
+      <c r="V14" t="s">
+        <v>3</v>
+      </c>
+      <c r="W14" t="s">
+        <v>3</v>
+      </c>
+      <c r="X14" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA14" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB14" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC14" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD14" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE14" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF14" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG14" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH14" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI14" t="s">
+        <v>3</v>
+      </c>
+      <c r="AJ14" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK14" t="s">
+        <v>3</v>
+      </c>
+      <c r="AL14" t="s">
+        <v>3</v>
+      </c>
+      <c r="AM14" t="s">
+        <v>3</v>
+      </c>
+      <c r="AN14" t="s">
+        <v>3</v>
+      </c>
+      <c r="AO14" t="s">
+        <v>3</v>
+      </c>
+      <c r="AP14" t="s">
+        <v>3</v>
+      </c>
+      <c r="AQ14" t="s">
+        <v>3</v>
+      </c>
+      <c r="AR14" t="s">
+        <v>3</v>
+      </c>
+      <c r="AS14" t="s">
+        <v>3</v>
+      </c>
+      <c r="AT14" t="s">
+        <v>3</v>
+      </c>
+      <c r="AU14" t="s">
+        <v>3</v>
+      </c>
+      <c r="AV14" t="s">
+        <v>3</v>
+      </c>
+      <c r="AW14" t="s">
+        <v>3</v>
+      </c>
+      <c r="AX14" t="s">
+        <v>3</v>
+      </c>
+      <c r="AY14" t="s">
+        <v>3</v>
+      </c>
+      <c r="AZ14" t="s">
+        <v>3</v>
+      </c>
+      <c r="BA14" t="s">
+        <v>3</v>
+      </c>
+      <c r="BB14" t="s">
+        <v>3</v>
+      </c>
+      <c r="BC14" t="s">
+        <v>3</v>
+      </c>
+      <c r="BD14" t="s">
+        <v>3</v>
+      </c>
+      <c r="BE14" t="s">
+        <v>3</v>
+      </c>
+      <c r="BF14" t="s">
+        <v>3</v>
+      </c>
+      <c r="BG14" t="s">
+        <v>3</v>
+      </c>
+      <c r="BH14" t="s">
+        <v>3</v>
+      </c>
+      <c r="BI14" t="s">
+        <v>3</v>
+      </c>
+      <c r="BJ14" t="s">
+        <v>3</v>
+      </c>
+      <c r="BK14" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="2:63" x14ac:dyDescent="0.4">
+      <c r="B15" s="2">
+        <v>0.99930555555555556</v>
+      </c>
+      <c r="C15" t="s">
+        <v>424</v>
+      </c>
+      <c r="D15" t="s">
+        <v>425</v>
+      </c>
+      <c r="E15" t="s">
+        <v>426</v>
+      </c>
+      <c r="F15" t="s">
+        <v>427</v>
+      </c>
+      <c r="G15" t="s">
+        <v>428</v>
+      </c>
+      <c r="H15" t="s">
+        <v>429</v>
+      </c>
+      <c r="I15" t="s">
+        <v>430</v>
+      </c>
+      <c r="J15" t="s">
+        <v>431</v>
+      </c>
+      <c r="K15" t="s">
+        <v>432</v>
+      </c>
+      <c r="L15" t="s">
+        <v>433</v>
+      </c>
+      <c r="M15" t="s">
+        <v>434</v>
+      </c>
+      <c r="N15" t="s">
+        <v>435</v>
+      </c>
+      <c r="O15" t="s">
+        <v>436</v>
+      </c>
+      <c r="P15" t="s">
+        <v>437</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>438</v>
+      </c>
+      <c r="R15" t="s">
+        <v>439</v>
+      </c>
+      <c r="S15" t="s">
+        <v>440</v>
+      </c>
+      <c r="T15" t="s">
+        <v>441</v>
+      </c>
+      <c r="U15" t="s">
+        <v>442</v>
+      </c>
+      <c r="V15" t="s">
+        <v>443</v>
+      </c>
+      <c r="W15" t="s">
+        <v>444</v>
+      </c>
+      <c r="X15" t="s">
+        <v>445</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>446</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>447</v>
+      </c>
+      <c r="AA15" t="s">
+        <v>448</v>
+      </c>
+      <c r="AB15" t="s">
+        <v>449</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>450</v>
+      </c>
+      <c r="AD15" t="s">
+        <v>451</v>
+      </c>
+      <c r="AE15" t="s">
+        <v>452</v>
+      </c>
+      <c r="AF15" t="s">
+        <v>453</v>
+      </c>
+      <c r="AG15" t="s">
+        <v>454</v>
+      </c>
+      <c r="AH15" t="s">
+        <v>455</v>
+      </c>
+      <c r="AI15" t="s">
+        <v>456</v>
+      </c>
+      <c r="AJ15" t="s">
+        <v>457</v>
+      </c>
+      <c r="AK15" t="s">
+        <v>458</v>
+      </c>
+      <c r="AL15" t="s">
+        <v>459</v>
+      </c>
+      <c r="AM15" t="s">
+        <v>460</v>
+      </c>
+      <c r="AN15" t="s">
+        <v>461</v>
+      </c>
+      <c r="AO15" t="s">
+        <v>462</v>
+      </c>
+      <c r="AP15" t="s">
+        <v>463</v>
+      </c>
+      <c r="AQ15" t="s">
+        <v>464</v>
+      </c>
+      <c r="AR15" t="s">
+        <v>465</v>
+      </c>
+      <c r="AS15" t="s">
+        <v>466</v>
+      </c>
+      <c r="AT15" t="s">
+        <v>467</v>
+      </c>
+      <c r="AU15" t="s">
+        <v>468</v>
+      </c>
+      <c r="AV15" t="s">
+        <v>469</v>
+      </c>
+      <c r="AW15" t="s">
+        <v>470</v>
+      </c>
+      <c r="AX15" t="s">
+        <v>471</v>
+      </c>
+      <c r="AY15" t="s">
+        <v>472</v>
+      </c>
+      <c r="AZ15" t="s">
+        <v>473</v>
+      </c>
+      <c r="BA15" t="s">
+        <v>687</v>
+      </c>
+      <c r="BB15" t="s">
+        <v>688</v>
+      </c>
+      <c r="BC15" t="s">
+        <v>689</v>
+      </c>
+      <c r="BD15" t="s">
+        <v>690</v>
+      </c>
+      <c r="BE15" t="s">
+        <v>691</v>
+      </c>
+      <c r="BF15" t="s">
+        <v>692</v>
+      </c>
+      <c r="BG15" t="s">
+        <v>693</v>
+      </c>
+      <c r="BH15" t="s">
+        <v>694</v>
+      </c>
+      <c r="BI15" t="s">
+        <v>695</v>
+      </c>
+      <c r="BJ15" t="s">
+        <v>696</v>
+      </c>
+      <c r="BK15" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="16" spans="2:63" x14ac:dyDescent="0.4">
+      <c r="B16" s="2">
+        <v>0</v>
+      </c>
+      <c r="C16" t="s">
+        <v>474</v>
+      </c>
+      <c r="D16" t="s">
+        <v>475</v>
+      </c>
+      <c r="E16" t="s">
+        <v>476</v>
+      </c>
+      <c r="F16" t="s">
+        <v>477</v>
+      </c>
+      <c r="G16" t="s">
+        <v>478</v>
+      </c>
+      <c r="H16" t="s">
+        <v>479</v>
+      </c>
+      <c r="I16" t="s">
+        <v>480</v>
+      </c>
+      <c r="J16" t="s">
+        <v>481</v>
+      </c>
+      <c r="K16" t="s">
+        <v>482</v>
+      </c>
+      <c r="L16" t="s">
+        <v>483</v>
+      </c>
+      <c r="M16" t="s">
+        <v>484</v>
+      </c>
+      <c r="N16" t="s">
+        <v>485</v>
+      </c>
+      <c r="O16" t="s">
+        <v>486</v>
+      </c>
+      <c r="P16" t="s">
+        <v>487</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>488</v>
+      </c>
+      <c r="R16" t="s">
+        <v>489</v>
+      </c>
+      <c r="S16" t="s">
+        <v>490</v>
+      </c>
+      <c r="T16" t="s">
+        <v>491</v>
+      </c>
+      <c r="U16" t="s">
+        <v>492</v>
+      </c>
+      <c r="V16" t="s">
+        <v>493</v>
+      </c>
+      <c r="W16" t="s">
+        <v>494</v>
+      </c>
+      <c r="X16" t="s">
+        <v>495</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>496</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>497</v>
+      </c>
+      <c r="AA16" t="s">
+        <v>498</v>
+      </c>
+      <c r="AB16" t="s">
+        <v>499</v>
+      </c>
+      <c r="AC16" t="s">
+        <v>500</v>
+      </c>
+      <c r="AD16" t="s">
+        <v>501</v>
+      </c>
+      <c r="AE16" t="s">
+        <v>502</v>
+      </c>
+      <c r="AF16" t="s">
+        <v>503</v>
+      </c>
+      <c r="AG16" t="s">
+        <v>504</v>
+      </c>
+      <c r="AH16" t="s">
+        <v>505</v>
+      </c>
+      <c r="AI16" t="s">
+        <v>506</v>
+      </c>
+      <c r="AJ16" t="s">
+        <v>507</v>
+      </c>
+      <c r="AK16" t="s">
+        <v>508</v>
+      </c>
+      <c r="AL16" t="s">
+        <v>509</v>
+      </c>
+      <c r="AM16" t="s">
+        <v>510</v>
+      </c>
+      <c r="AN16" t="s">
+        <v>511</v>
+      </c>
+      <c r="AO16" t="s">
+        <v>512</v>
+      </c>
+      <c r="AP16" t="s">
+        <v>513</v>
+      </c>
+      <c r="AQ16" t="s">
+        <v>514</v>
+      </c>
+      <c r="AR16" t="s">
+        <v>515</v>
+      </c>
+      <c r="AS16" t="s">
+        <v>516</v>
+      </c>
+      <c r="AT16" t="s">
+        <v>517</v>
+      </c>
+      <c r="AU16" t="s">
+        <v>518</v>
+      </c>
+      <c r="AV16" t="s">
+        <v>519</v>
+      </c>
+      <c r="AW16" t="s">
+        <v>520</v>
+      </c>
+      <c r="AX16" t="s">
+        <v>521</v>
+      </c>
+      <c r="AY16" t="s">
+        <v>522</v>
+      </c>
+      <c r="AZ16" t="s">
+        <v>523</v>
+      </c>
+      <c r="BA16" t="s">
+        <v>698</v>
+      </c>
+      <c r="BB16" t="s">
+        <v>699</v>
+      </c>
+      <c r="BC16" t="s">
+        <v>700</v>
+      </c>
+      <c r="BD16" t="s">
+        <v>701</v>
+      </c>
+      <c r="BE16" t="s">
+        <v>702</v>
+      </c>
+      <c r="BF16" t="s">
+        <v>703</v>
+      </c>
+      <c r="BG16" t="s">
+        <v>704</v>
+      </c>
+      <c r="BH16" t="s">
+        <v>705</v>
+      </c>
+      <c r="BI16" t="s">
+        <v>706</v>
+      </c>
+      <c r="BJ16" t="s">
+        <v>707</v>
+      </c>
+      <c r="BK16" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="17" spans="2:63" x14ac:dyDescent="0.4">
+      <c r="B17" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C17" t="s">
+        <v>3</v>
+      </c>
+      <c r="D17" t="s">
+        <v>3</v>
+      </c>
+      <c r="E17" t="s">
+        <v>3</v>
+      </c>
+      <c r="F17" t="s">
+        <v>3</v>
+      </c>
+      <c r="G17" t="s">
+        <v>3</v>
+      </c>
+      <c r="H17" t="s">
+        <v>3</v>
+      </c>
+      <c r="I17" t="s">
+        <v>3</v>
+      </c>
+      <c r="J17" t="s">
+        <v>3</v>
+      </c>
+      <c r="K17" t="s">
+        <v>3</v>
+      </c>
+      <c r="L17" t="s">
+        <v>3</v>
+      </c>
+      <c r="M17" t="s">
+        <v>3</v>
+      </c>
+      <c r="N17" t="s">
+        <v>3</v>
+      </c>
+      <c r="O17" t="s">
+        <v>3</v>
+      </c>
+      <c r="P17" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>3</v>
+      </c>
+      <c r="R17" t="s">
+        <v>3</v>
+      </c>
+      <c r="S17" t="s">
+        <v>3</v>
+      </c>
+      <c r="T17" t="s">
+        <v>3</v>
+      </c>
+      <c r="U17" t="s">
+        <v>3</v>
+      </c>
+      <c r="V17" t="s">
+        <v>3</v>
+      </c>
+      <c r="W17" t="s">
+        <v>3</v>
+      </c>
+      <c r="X17" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA17" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB17" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC17" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD17" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE17" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF17" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG17" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH17" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI17" t="s">
+        <v>3</v>
+      </c>
+      <c r="AJ17" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK17" t="s">
+        <v>3</v>
+      </c>
+      <c r="AL17" t="s">
+        <v>3</v>
+      </c>
+      <c r="AM17" t="s">
+        <v>3</v>
+      </c>
+      <c r="AN17" t="s">
+        <v>3</v>
+      </c>
+      <c r="AO17" t="s">
+        <v>3</v>
+      </c>
+      <c r="AP17" t="s">
+        <v>3</v>
+      </c>
+      <c r="AQ17" t="s">
+        <v>3</v>
+      </c>
+      <c r="AR17" t="s">
+        <v>3</v>
+      </c>
+      <c r="AS17" t="s">
+        <v>3</v>
+      </c>
+      <c r="AT17" t="s">
+        <v>3</v>
+      </c>
+      <c r="AU17" t="s">
+        <v>3</v>
+      </c>
+      <c r="AV17" t="s">
+        <v>3</v>
+      </c>
+      <c r="AW17" t="s">
+        <v>3</v>
+      </c>
+      <c r="AX17" t="s">
+        <v>3</v>
+      </c>
+      <c r="AY17" t="s">
+        <v>3</v>
+      </c>
+      <c r="AZ17" t="s">
+        <v>3</v>
+      </c>
+      <c r="BA17" t="s">
+        <v>3</v>
+      </c>
+      <c r="BB17" t="s">
+        <v>3</v>
+      </c>
+      <c r="BC17" t="s">
+        <v>3</v>
+      </c>
+      <c r="BD17" t="s">
+        <v>3</v>
+      </c>
+      <c r="BE17" t="s">
+        <v>3</v>
+      </c>
+      <c r="BF17" t="s">
+        <v>3</v>
+      </c>
+      <c r="BG17" t="s">
+        <v>3</v>
+      </c>
+      <c r="BH17" t="s">
+        <v>3</v>
+      </c>
+      <c r="BI17" t="s">
+        <v>3</v>
+      </c>
+      <c r="BJ17" t="s">
+        <v>3</v>
+      </c>
+      <c r="BK17" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="2:63" x14ac:dyDescent="0.4">
+      <c r="B18" s="2">
+        <v>0.16597222222222222</v>
+      </c>
+      <c r="C18" t="s">
+        <v>4</v>
+      </c>
+      <c r="D18" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" t="s">
+        <v>17</v>
+      </c>
+      <c r="F18" t="s">
+        <v>18</v>
+      </c>
+      <c r="G18" t="s">
+        <v>19</v>
+      </c>
+      <c r="H18" t="s">
+        <v>20</v>
+      </c>
+      <c r="I18" t="s">
+        <v>380</v>
+      </c>
+      <c r="J18" t="s">
+        <v>381</v>
+      </c>
+      <c r="K18" t="s">
+        <v>382</v>
+      </c>
+      <c r="L18" t="s">
+        <v>383</v>
+      </c>
+      <c r="M18" t="s">
+        <v>384</v>
+      </c>
+      <c r="N18" t="s">
+        <v>385</v>
+      </c>
+      <c r="O18" t="s">
+        <v>386</v>
+      </c>
+      <c r="P18" t="s">
+        <v>387</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>388</v>
+      </c>
+      <c r="R18" t="s">
+        <v>389</v>
+      </c>
+      <c r="S18" t="s">
+        <v>390</v>
+      </c>
+      <c r="T18" t="s">
+        <v>391</v>
+      </c>
+      <c r="U18" t="s">
+        <v>392</v>
+      </c>
+      <c r="V18" t="s">
+        <v>393</v>
+      </c>
+      <c r="W18" t="s">
+        <v>394</v>
+      </c>
+      <c r="X18" t="s">
+        <v>395</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>396</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>397</v>
+      </c>
+      <c r="AA18" t="s">
+        <v>398</v>
+      </c>
+      <c r="AB18" t="s">
+        <v>399</v>
+      </c>
+      <c r="AC18" t="s">
+        <v>400</v>
+      </c>
+      <c r="AD18" t="s">
+        <v>401</v>
+      </c>
+      <c r="AE18" t="s">
+        <v>402</v>
+      </c>
+      <c r="AF18" t="s">
+        <v>403</v>
+      </c>
+      <c r="AG18" t="s">
+        <v>404</v>
+      </c>
+      <c r="AH18" t="s">
+        <v>405</v>
+      </c>
+      <c r="AI18" t="s">
+        <v>406</v>
+      </c>
+      <c r="AJ18" t="s">
+        <v>407</v>
+      </c>
+      <c r="AK18" t="s">
+        <v>408</v>
+      </c>
+      <c r="AL18" t="s">
+        <v>409</v>
+      </c>
+      <c r="AM18" t="s">
+        <v>410</v>
+      </c>
+      <c r="AN18" t="s">
+        <v>411</v>
+      </c>
+      <c r="AO18" t="s">
+        <v>412</v>
+      </c>
+      <c r="AP18" t="s">
+        <v>413</v>
+      </c>
+      <c r="AQ18" t="s">
+        <v>414</v>
+      </c>
+      <c r="AR18" t="s">
+        <v>415</v>
+      </c>
+      <c r="AS18" t="s">
+        <v>416</v>
+      </c>
+      <c r="AT18" t="s">
+        <v>417</v>
+      </c>
+      <c r="AU18" t="s">
+        <v>418</v>
+      </c>
+      <c r="AV18" t="s">
+        <v>419</v>
+      </c>
+      <c r="AW18" t="s">
+        <v>420</v>
+      </c>
+      <c r="AX18" t="s">
+        <v>421</v>
+      </c>
+      <c r="AY18" t="s">
+        <v>422</v>
+      </c>
+      <c r="AZ18" t="s">
+        <v>423</v>
+      </c>
+      <c r="BA18" t="s">
+        <v>709</v>
+      </c>
+      <c r="BB18" t="s">
+        <v>710</v>
+      </c>
+      <c r="BC18" t="s">
+        <v>711</v>
+      </c>
+      <c r="BD18" t="s">
+        <v>712</v>
+      </c>
+      <c r="BE18" t="s">
+        <v>713</v>
+      </c>
+      <c r="BF18" t="s">
+        <v>714</v>
+      </c>
+      <c r="BG18" t="s">
+        <v>715</v>
+      </c>
+      <c r="BH18" t="s">
+        <v>716</v>
+      </c>
+      <c r="BI18" t="s">
+        <v>717</v>
+      </c>
+      <c r="BJ18" t="s">
+        <v>718</v>
+      </c>
+      <c r="BK18" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="20" spans="2:63" x14ac:dyDescent="0.4">
+      <c r="B20" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C20" s="7"/>
+      <c r="D20" s="14"/>
+    </row>
+    <row r="21" spans="2:63" x14ac:dyDescent="0.4">
+      <c r="B21" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="C21" s="12">
+        <v>15</v>
+      </c>
+      <c r="D21" s="17" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="22" spans="2:63" x14ac:dyDescent="0.4">
+      <c r="B22" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="C22" s="12">
+        <v>20</v>
+      </c>
+      <c r="D22" s="15" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="23" spans="2:63" x14ac:dyDescent="0.4">
+      <c r="B23" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C23" s="8">
+        <v>1</v>
+      </c>
+      <c r="D23" s="19" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="24" spans="2:63" x14ac:dyDescent="0.4">
+      <c r="B24" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C24" s="8">
+        <v>2</v>
+      </c>
+      <c r="D24" s="20" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="25" spans="2:63" x14ac:dyDescent="0.4">
+      <c r="B25" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C25" s="8">
+        <v>3</v>
+      </c>
+      <c r="D25" s="18" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="26" spans="2:63" s="5" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="B26" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="C26" s="8">
+        <v>4</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="27" spans="2:63" s="5" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="B27" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="C27" s="12">
+        <v>16</v>
+      </c>
+      <c r="D27" s="16" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="28" spans="2:63" s="5" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="B28" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="C28" s="8">
+        <v>0</v>
+      </c>
+      <c r="D28" s="16" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="29" spans="2:63" s="5" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="B29" t="s">
+        <v>39</v>
+      </c>
+      <c r="C29" s="6"/>
+    </row>
+    <row r="30" spans="2:63" s="5" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="B30" t="s">
+        <v>25</v>
+      </c>
+      <c r="C30" s="6"/>
+    </row>
+    <row r="31" spans="2:63" s="5" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="B31" s="6"/>
+      <c r="C31" s="6"/>
+    </row>
+    <row r="32" spans="2:63" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="B32" s="6" t="s">
         <v>63</v>
       </c>

--- a/docs/光和稼働データ収集装置デバイスマップ.xlsx
+++ b/docs/光和稼働データ収集装置デバイスマップ.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myProgram\GitHub\ForMitsuwa\factory_visualize_server_atmw\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD1138D1-3B40-4B31-9099-814B526CD1F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DB67241-87C3-4473-86AA-91543A1E1618}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{2B542973-F752-4A81-A420-BFC37E5D0A51}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{2B542973-F752-4A81-A420-BFC37E5D0A51}"/>
   </bookViews>
   <sheets>
     <sheet name="旧割付" sheetId="1" r:id="rId1"/>
     <sheet name="20260622" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -2789,11 +2789,11 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2842,8 +2842,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF24D642"/>
       <color rgb="FFFF66CC"/>
-      <color rgb="FF24D642"/>
       <color rgb="FFFF99CC"/>
       <color rgb="FF0000FF"/>
     </mruColors>
@@ -5744,7 +5744,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:63" x14ac:dyDescent="0.4">
-      <c r="B1" s="23" t="s">
+      <c r="B1" s="22" t="s">
         <v>570</v>
       </c>
       <c r="C1" t="s">
@@ -6123,43 +6123,43 @@
       <c r="B3" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="C3" s="22" t="s">
+      <c r="C3" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="D3" s="22" t="s">
+      <c r="D3" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="E3" s="22" t="s">
+      <c r="E3" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="F3" s="22" t="s">
+      <c r="F3" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="G3" s="22" t="s">
+      <c r="G3" s="10" t="s">
         <v>524</v>
       </c>
-      <c r="H3" s="22" t="s">
+      <c r="H3" s="10" t="s">
         <v>525</v>
       </c>
-      <c r="I3" s="22" t="s">
+      <c r="I3" s="10" t="s">
         <v>526</v>
       </c>
-      <c r="J3" s="22" t="s">
+      <c r="J3" s="10" t="s">
         <v>527</v>
       </c>
-      <c r="K3" s="22" t="s">
+      <c r="K3" s="10" t="s">
         <v>528</v>
       </c>
-      <c r="L3" s="22" t="s">
+      <c r="L3" s="10" t="s">
         <v>529</v>
       </c>
-      <c r="M3" s="22" t="s">
+      <c r="M3" s="10" t="s">
         <v>530</v>
       </c>
-      <c r="N3" s="22" t="s">
+      <c r="N3" s="10" t="s">
         <v>531</v>
       </c>
-      <c r="O3" s="22" t="s">
+      <c r="O3" s="10" t="s">
         <v>532</v>
       </c>
       <c r="P3" s="21" t="s">
@@ -6192,13 +6192,13 @@
       <c r="Y3" s="21" t="s">
         <v>627</v>
       </c>
-      <c r="Z3" s="10" t="s">
-        <v>541</v>
-      </c>
-      <c r="AA3" s="22" t="s">
+      <c r="Z3" s="21" t="s">
+        <v>561</v>
+      </c>
+      <c r="AA3" s="10" t="s">
         <v>542</v>
       </c>
-      <c r="AB3" s="22" t="s">
+      <c r="AB3" s="10" t="s">
         <v>543</v>
       </c>
       <c r="AC3" s="21" t="s">
@@ -6216,40 +6216,40 @@
       <c r="AG3" s="21" t="s">
         <v>628</v>
       </c>
-      <c r="AH3" s="22" t="s">
+      <c r="AH3" s="10" t="s">
         <v>549</v>
       </c>
-      <c r="AI3" s="22" t="s">
+      <c r="AI3" s="10" t="s">
         <v>550</v>
       </c>
       <c r="AJ3" s="21" t="s">
         <v>561</v>
       </c>
-      <c r="AK3" s="22" t="s">
+      <c r="AK3" s="10" t="s">
         <v>551</v>
       </c>
-      <c r="AL3" s="22" t="s">
+      <c r="AL3" s="10" t="s">
         <v>620</v>
       </c>
       <c r="AM3" s="21" t="s">
         <v>619</v>
       </c>
-      <c r="AN3" s="22" t="s">
+      <c r="AN3" s="10" t="s">
         <v>621</v>
       </c>
-      <c r="AO3" s="22" t="s">
+      <c r="AO3" s="10" t="s">
         <v>622</v>
       </c>
-      <c r="AP3" s="22" t="s">
+      <c r="AP3" s="10" t="s">
         <v>623</v>
       </c>
-      <c r="AQ3" s="22" t="s">
+      <c r="AQ3" s="10" t="s">
         <v>624</v>
       </c>
-      <c r="AR3" s="22" t="s">
+      <c r="AR3" s="10" t="s">
         <v>559</v>
       </c>
-      <c r="AS3" s="22" t="s">
+      <c r="AS3" s="10" t="s">
         <v>560</v>
       </c>
       <c r="AT3" s="21" t="s">
@@ -6311,187 +6311,187 @@
       <c r="B4" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" s="23" t="s">
         <v>110</v>
       </c>
-      <c r="J4" t="s">
+      <c r="J4" s="23" t="s">
         <v>113</v>
       </c>
-      <c r="K4" t="s">
+      <c r="K4" s="23" t="s">
         <v>116</v>
       </c>
-      <c r="L4" t="s">
+      <c r="L4" s="23" t="s">
         <v>117</v>
       </c>
-      <c r="M4" t="s">
+      <c r="M4" s="23" t="s">
         <v>118</v>
       </c>
-      <c r="N4" t="s">
+      <c r="N4" s="23" t="s">
         <v>119</v>
       </c>
-      <c r="O4" t="s">
+      <c r="O4" s="23" t="s">
         <v>120</v>
       </c>
-      <c r="P4" t="s">
+      <c r="P4" s="23" t="s">
         <v>121</v>
       </c>
-      <c r="Q4" t="s">
+      <c r="Q4" s="23" t="s">
         <v>122</v>
       </c>
-      <c r="R4" t="s">
+      <c r="R4" s="23" t="s">
         <v>123</v>
       </c>
-      <c r="S4" t="s">
+      <c r="S4" s="23" t="s">
         <v>124</v>
       </c>
-      <c r="T4" t="s">
+      <c r="T4" s="23" t="s">
         <v>125</v>
       </c>
-      <c r="U4" t="s">
+      <c r="U4" s="23" t="s">
         <v>126</v>
       </c>
-      <c r="V4" t="s">
+      <c r="V4" s="23" t="s">
         <v>127</v>
       </c>
-      <c r="W4" t="s">
+      <c r="W4" s="23" t="s">
         <v>128</v>
       </c>
-      <c r="X4" t="s">
+      <c r="X4" s="23" t="s">
         <v>129</v>
       </c>
-      <c r="Y4" t="s">
+      <c r="Y4" s="23" t="s">
         <v>130</v>
       </c>
-      <c r="Z4" t="s">
+      <c r="Z4" s="23" t="s">
         <v>131</v>
       </c>
-      <c r="AA4" t="s">
+      <c r="AA4" s="23" t="s">
         <v>132</v>
       </c>
-      <c r="AB4" t="s">
+      <c r="AB4" s="23" t="s">
         <v>133</v>
       </c>
-      <c r="AC4" t="s">
+      <c r="AC4" s="23" t="s">
         <v>134</v>
       </c>
-      <c r="AD4" t="s">
+      <c r="AD4" s="23" t="s">
         <v>135</v>
       </c>
-      <c r="AE4" t="s">
+      <c r="AE4" s="23" t="s">
         <v>136</v>
       </c>
-      <c r="AF4" t="s">
+      <c r="AF4" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="AG4" t="s">
+      <c r="AG4" s="23" t="s">
         <v>138</v>
       </c>
-      <c r="AH4" t="s">
+      <c r="AH4" s="23" t="s">
         <v>139</v>
       </c>
-      <c r="AI4" t="s">
+      <c r="AI4" s="23" t="s">
         <v>140</v>
       </c>
-      <c r="AJ4" t="s">
+      <c r="AJ4" s="23" t="s">
         <v>141</v>
       </c>
-      <c r="AK4" t="s">
+      <c r="AK4" s="23" t="s">
         <v>142</v>
       </c>
-      <c r="AL4" t="s">
+      <c r="AL4" s="23" t="s">
         <v>143</v>
       </c>
-      <c r="AM4" t="s">
+      <c r="AM4" s="23" t="s">
         <v>144</v>
       </c>
-      <c r="AN4" t="s">
+      <c r="AN4" s="23" t="s">
         <v>145</v>
       </c>
-      <c r="AO4" t="s">
+      <c r="AO4" s="23" t="s">
         <v>146</v>
       </c>
-      <c r="AP4" t="s">
+      <c r="AP4" s="23" t="s">
         <v>147</v>
       </c>
-      <c r="AQ4" t="s">
+      <c r="AQ4" s="23" t="s">
         <v>148</v>
       </c>
-      <c r="AR4" t="s">
+      <c r="AR4" s="23" t="s">
         <v>223</v>
       </c>
-      <c r="AS4" t="s">
+      <c r="AS4" s="23" t="s">
         <v>224</v>
       </c>
-      <c r="AT4" t="s">
+      <c r="AT4" s="23" t="s">
         <v>225</v>
       </c>
-      <c r="AU4" t="s">
+      <c r="AU4" s="23" t="s">
         <v>226</v>
       </c>
-      <c r="AV4" t="s">
+      <c r="AV4" s="23" t="s">
         <v>227</v>
       </c>
-      <c r="AW4" t="s">
+      <c r="AW4" s="23" t="s">
         <v>228</v>
       </c>
-      <c r="AX4" t="s">
+      <c r="AX4" s="23" t="s">
         <v>229</v>
       </c>
-      <c r="AY4" t="s">
+      <c r="AY4" s="23" t="s">
         <v>230</v>
       </c>
-      <c r="AZ4" t="s">
+      <c r="AZ4" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="BA4" t="s">
+      <c r="BA4" s="23" t="s">
         <v>720</v>
       </c>
-      <c r="BB4" t="s">
+      <c r="BB4" s="23" t="s">
         <v>721</v>
       </c>
-      <c r="BC4" t="s">
+      <c r="BC4" s="23" t="s">
         <v>722</v>
       </c>
-      <c r="BD4" t="s">
+      <c r="BD4" s="23" t="s">
         <v>723</v>
       </c>
-      <c r="BE4" t="s">
+      <c r="BE4" s="23" t="s">
         <v>724</v>
       </c>
-      <c r="BF4" t="s">
+      <c r="BF4" s="23" t="s">
         <v>725</v>
       </c>
-      <c r="BG4" t="s">
+      <c r="BG4" s="23" t="s">
         <v>726</v>
       </c>
-      <c r="BH4" t="s">
+      <c r="BH4" s="23" t="s">
         <v>727</v>
       </c>
-      <c r="BI4" t="s">
+      <c r="BI4" s="23" t="s">
         <v>728</v>
       </c>
-      <c r="BJ4" t="s">
+      <c r="BJ4" s="23" t="s">
         <v>729</v>
       </c>
-      <c r="BK4" t="s">
+      <c r="BK4" s="23" t="s">
         <v>730</v>
       </c>
     </row>
@@ -6499,187 +6499,187 @@
       <c r="B5" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" s="23" t="s">
         <v>111</v>
       </c>
-      <c r="J5" t="s">
+      <c r="J5" s="23" t="s">
         <v>114</v>
       </c>
-      <c r="K5" t="s">
+      <c r="K5" s="23" t="s">
         <v>149</v>
       </c>
-      <c r="L5" t="s">
+      <c r="L5" s="23" t="s">
         <v>150</v>
       </c>
-      <c r="M5" t="s">
+      <c r="M5" s="23" t="s">
         <v>151</v>
       </c>
-      <c r="N5" t="s">
+      <c r="N5" s="23" t="s">
         <v>152</v>
       </c>
-      <c r="O5" t="s">
+      <c r="O5" s="23" t="s">
         <v>153</v>
       </c>
-      <c r="P5" t="s">
+      <c r="P5" s="23" t="s">
         <v>154</v>
       </c>
-      <c r="Q5" t="s">
+      <c r="Q5" s="23" t="s">
         <v>155</v>
       </c>
-      <c r="R5" t="s">
+      <c r="R5" s="23" t="s">
         <v>156</v>
       </c>
-      <c r="S5" t="s">
+      <c r="S5" s="23" t="s">
         <v>157</v>
       </c>
-      <c r="T5" t="s">
+      <c r="T5" s="23" t="s">
         <v>158</v>
       </c>
-      <c r="U5" t="s">
+      <c r="U5" s="23" t="s">
         <v>159</v>
       </c>
-      <c r="V5" t="s">
+      <c r="V5" s="23" t="s">
         <v>160</v>
       </c>
-      <c r="W5" t="s">
+      <c r="W5" s="23" t="s">
         <v>161</v>
       </c>
-      <c r="X5" t="s">
+      <c r="X5" s="23" t="s">
         <v>162</v>
       </c>
-      <c r="Y5" t="s">
+      <c r="Y5" s="23" t="s">
         <v>163</v>
       </c>
-      <c r="Z5" t="s">
+      <c r="Z5" s="23" t="s">
         <v>164</v>
       </c>
-      <c r="AA5" t="s">
+      <c r="AA5" s="23" t="s">
         <v>165</v>
       </c>
-      <c r="AB5" t="s">
+      <c r="AB5" s="23" t="s">
         <v>166</v>
       </c>
-      <c r="AC5" t="s">
+      <c r="AC5" s="23" t="s">
         <v>167</v>
       </c>
-      <c r="AD5" t="s">
+      <c r="AD5" s="23" t="s">
         <v>168</v>
       </c>
-      <c r="AE5" t="s">
+      <c r="AE5" s="23" t="s">
         <v>169</v>
       </c>
-      <c r="AF5" t="s">
+      <c r="AF5" s="23" t="s">
         <v>170</v>
       </c>
-      <c r="AG5" t="s">
+      <c r="AG5" s="23" t="s">
         <v>171</v>
       </c>
-      <c r="AH5" t="s">
+      <c r="AH5" s="23" t="s">
         <v>172</v>
       </c>
-      <c r="AI5" t="s">
+      <c r="AI5" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="AJ5" t="s">
+      <c r="AJ5" s="23" t="s">
         <v>174</v>
       </c>
-      <c r="AK5" t="s">
+      <c r="AK5" s="23" t="s">
         <v>175</v>
       </c>
-      <c r="AL5" t="s">
+      <c r="AL5" s="23" t="s">
         <v>176</v>
       </c>
-      <c r="AM5" t="s">
+      <c r="AM5" s="23" t="s">
         <v>177</v>
       </c>
-      <c r="AN5" t="s">
+      <c r="AN5" s="23" t="s">
         <v>178</v>
       </c>
-      <c r="AO5" t="s">
+      <c r="AO5" s="23" t="s">
         <v>179</v>
       </c>
-      <c r="AP5" t="s">
+      <c r="AP5" s="23" t="s">
         <v>180</v>
       </c>
-      <c r="AQ5" t="s">
+      <c r="AQ5" s="23" t="s">
         <v>181</v>
       </c>
-      <c r="AR5" t="s">
+      <c r="AR5" s="23" t="s">
         <v>231</v>
       </c>
-      <c r="AS5" t="s">
+      <c r="AS5" s="23" t="s">
         <v>232</v>
       </c>
-      <c r="AT5" t="s">
+      <c r="AT5" s="23" t="s">
         <v>233</v>
       </c>
-      <c r="AU5" t="s">
+      <c r="AU5" s="23" t="s">
         <v>234</v>
       </c>
-      <c r="AV5" t="s">
+      <c r="AV5" s="23" t="s">
         <v>235</v>
       </c>
-      <c r="AW5" t="s">
+      <c r="AW5" s="23" t="s">
         <v>236</v>
       </c>
-      <c r="AX5" t="s">
+      <c r="AX5" s="23" t="s">
         <v>237</v>
       </c>
-      <c r="AY5" t="s">
+      <c r="AY5" s="23" t="s">
         <v>238</v>
       </c>
-      <c r="AZ5" t="s">
+      <c r="AZ5" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="BA5" t="s">
+      <c r="BA5" s="23" t="s">
         <v>731</v>
       </c>
-      <c r="BB5" t="s">
+      <c r="BB5" s="23" t="s">
         <v>732</v>
       </c>
-      <c r="BC5" t="s">
+      <c r="BC5" s="23" t="s">
         <v>733</v>
       </c>
-      <c r="BD5" t="s">
+      <c r="BD5" s="23" t="s">
         <v>734</v>
       </c>
-      <c r="BE5" t="s">
+      <c r="BE5" s="23" t="s">
         <v>735</v>
       </c>
-      <c r="BF5" t="s">
+      <c r="BF5" s="23" t="s">
         <v>736</v>
       </c>
-      <c r="BG5" t="s">
+      <c r="BG5" s="23" t="s">
         <v>737</v>
       </c>
-      <c r="BH5" t="s">
+      <c r="BH5" s="23" t="s">
         <v>738</v>
       </c>
-      <c r="BI5" t="s">
+      <c r="BI5" s="23" t="s">
         <v>739</v>
       </c>
-      <c r="BJ5" t="s">
+      <c r="BJ5" s="23" t="s">
         <v>740</v>
       </c>
-      <c r="BK5" t="s">
+      <c r="BK5" s="23" t="s">
         <v>741</v>
       </c>
     </row>
@@ -6687,380 +6687,504 @@
       <c r="B6" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="H6" t="s">
+      <c r="H6" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="I6" t="s">
+      <c r="I6" s="23" t="s">
         <v>112</v>
       </c>
-      <c r="J6" t="s">
+      <c r="J6" s="23" t="s">
         <v>115</v>
       </c>
-      <c r="K6" t="s">
+      <c r="K6" s="23" t="s">
         <v>182</v>
       </c>
-      <c r="L6" t="s">
+      <c r="L6" s="23" t="s">
         <v>183</v>
       </c>
-      <c r="M6" t="s">
+      <c r="M6" s="23" t="s">
         <v>184</v>
       </c>
-      <c r="N6" t="s">
+      <c r="N6" s="23" t="s">
         <v>185</v>
       </c>
-      <c r="O6" t="s">
+      <c r="O6" s="23" t="s">
         <v>186</v>
       </c>
-      <c r="P6" t="s">
+      <c r="P6" s="23" t="s">
         <v>187</v>
       </c>
-      <c r="Q6" t="s">
+      <c r="Q6" s="23" t="s">
         <v>188</v>
       </c>
-      <c r="R6" t="s">
+      <c r="R6" s="23" t="s">
         <v>189</v>
       </c>
-      <c r="S6" t="s">
+      <c r="S6" s="23" t="s">
         <v>190</v>
       </c>
-      <c r="T6" t="s">
+      <c r="T6" s="23" t="s">
         <v>191</v>
       </c>
-      <c r="U6" t="s">
+      <c r="U6" s="23" t="s">
         <v>192</v>
       </c>
-      <c r="V6" t="s">
+      <c r="V6" s="23" t="s">
         <v>193</v>
       </c>
-      <c r="W6" t="s">
+      <c r="W6" s="23" t="s">
         <v>194</v>
       </c>
-      <c r="X6" t="s">
+      <c r="X6" s="23" t="s">
         <v>195</v>
       </c>
-      <c r="Y6" t="s">
+      <c r="Y6" s="23" t="s">
         <v>196</v>
       </c>
-      <c r="Z6" t="s">
+      <c r="Z6" s="23" t="s">
         <v>197</v>
       </c>
-      <c r="AA6" t="s">
+      <c r="AA6" s="23" t="s">
         <v>198</v>
       </c>
-      <c r="AB6" t="s">
+      <c r="AB6" s="23" t="s">
         <v>199</v>
       </c>
-      <c r="AC6" t="s">
+      <c r="AC6" s="23" t="s">
         <v>200</v>
       </c>
-      <c r="AD6" t="s">
+      <c r="AD6" s="23" t="s">
         <v>201</v>
       </c>
-      <c r="AE6" t="s">
+      <c r="AE6" s="23" t="s">
         <v>202</v>
       </c>
-      <c r="AF6" t="s">
+      <c r="AF6" s="23" t="s">
         <v>203</v>
       </c>
-      <c r="AG6" t="s">
+      <c r="AG6" s="23" t="s">
         <v>204</v>
       </c>
-      <c r="AH6" t="s">
+      <c r="AH6" s="23" t="s">
         <v>205</v>
       </c>
-      <c r="AI6" t="s">
+      <c r="AI6" s="23" t="s">
         <v>206</v>
       </c>
-      <c r="AJ6" t="s">
+      <c r="AJ6" s="23" t="s">
         <v>207</v>
       </c>
-      <c r="AK6" t="s">
+      <c r="AK6" s="23" t="s">
         <v>208</v>
       </c>
-      <c r="AL6" t="s">
+      <c r="AL6" s="23" t="s">
         <v>209</v>
       </c>
-      <c r="AM6" t="s">
+      <c r="AM6" s="23" t="s">
         <v>210</v>
       </c>
-      <c r="AN6" t="s">
+      <c r="AN6" s="23" t="s">
         <v>211</v>
       </c>
-      <c r="AO6" t="s">
+      <c r="AO6" s="23" t="s">
         <v>212</v>
       </c>
-      <c r="AP6" t="s">
+      <c r="AP6" s="23" t="s">
         <v>213</v>
       </c>
-      <c r="AQ6" t="s">
+      <c r="AQ6" s="23" t="s">
         <v>214</v>
       </c>
-      <c r="AR6" t="s">
+      <c r="AR6" s="23" t="s">
         <v>239</v>
       </c>
-      <c r="AS6" t="s">
+      <c r="AS6" s="23" t="s">
         <v>240</v>
       </c>
-      <c r="AT6" t="s">
+      <c r="AT6" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="AU6" t="s">
+      <c r="AU6" s="23" t="s">
         <v>242</v>
       </c>
-      <c r="AV6" t="s">
+      <c r="AV6" s="23" t="s">
         <v>243</v>
       </c>
-      <c r="AW6" t="s">
+      <c r="AW6" s="23" t="s">
         <v>244</v>
       </c>
-      <c r="AX6" t="s">
+      <c r="AX6" s="23" t="s">
         <v>245</v>
       </c>
-      <c r="AY6" t="s">
+      <c r="AY6" s="23" t="s">
         <v>246</v>
       </c>
-      <c r="AZ6" t="s">
+      <c r="AZ6" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="BA6" t="s">
+      <c r="BA6" s="23" t="s">
         <v>742</v>
       </c>
-      <c r="BB6" t="s">
+      <c r="BB6" s="23" t="s">
         <v>743</v>
       </c>
-      <c r="BC6" t="s">
+      <c r="BC6" s="23" t="s">
         <v>744</v>
       </c>
-      <c r="BD6" t="s">
+      <c r="BD6" s="23" t="s">
         <v>745</v>
       </c>
-      <c r="BE6" t="s">
+      <c r="BE6" s="23" t="s">
         <v>746</v>
       </c>
-      <c r="BF6" t="s">
+      <c r="BF6" s="23" t="s">
         <v>747</v>
       </c>
-      <c r="BG6" t="s">
+      <c r="BG6" s="23" t="s">
         <v>748</v>
       </c>
-      <c r="BH6" t="s">
+      <c r="BH6" s="23" t="s">
         <v>749</v>
       </c>
-      <c r="BI6" t="s">
+      <c r="BI6" s="23" t="s">
         <v>750</v>
       </c>
-      <c r="BJ6" t="s">
+      <c r="BJ6" s="23" t="s">
         <v>751</v>
       </c>
-      <c r="BK6" t="s">
+      <c r="BK6" s="23" t="s">
         <v>752</v>
       </c>
+    </row>
+    <row r="7" spans="2:63" x14ac:dyDescent="0.4">
+      <c r="C7" s="23"/>
+      <c r="D7" s="23"/>
+      <c r="E7" s="23"/>
+      <c r="F7" s="23"/>
+      <c r="G7" s="23"/>
+      <c r="H7" s="23"/>
+      <c r="I7" s="23"/>
+      <c r="J7" s="23"/>
+      <c r="K7" s="23"/>
+      <c r="L7" s="23"/>
+      <c r="M7" s="23"/>
+      <c r="N7" s="23"/>
+      <c r="O7" s="23"/>
+      <c r="P7" s="23"/>
+      <c r="Q7" s="23"/>
+      <c r="R7" s="23"/>
+      <c r="S7" s="23"/>
+      <c r="T7" s="23"/>
+      <c r="U7" s="23"/>
+      <c r="V7" s="23"/>
+      <c r="W7" s="23"/>
+      <c r="X7" s="23"/>
+      <c r="Y7" s="23"/>
+      <c r="Z7" s="23"/>
+      <c r="AA7" s="23"/>
+      <c r="AB7" s="23"/>
+      <c r="AC7" s="23"/>
+      <c r="AD7" s="23"/>
+      <c r="AE7" s="23"/>
+      <c r="AF7" s="23"/>
+      <c r="AG7" s="23"/>
+      <c r="AH7" s="23"/>
+      <c r="AI7" s="23"/>
+      <c r="AJ7" s="23"/>
+      <c r="AK7" s="23"/>
+      <c r="AL7" s="23"/>
+      <c r="AM7" s="23"/>
+      <c r="AN7" s="23"/>
+      <c r="AO7" s="23"/>
+      <c r="AP7" s="23"/>
+      <c r="AQ7" s="23"/>
+      <c r="AR7" s="23"/>
+      <c r="AS7" s="23"/>
+      <c r="AT7" s="23"/>
+      <c r="AU7" s="23"/>
+      <c r="AV7" s="23"/>
+      <c r="AW7" s="23"/>
+      <c r="AX7" s="23"/>
+      <c r="AY7" s="23"/>
+      <c r="AZ7" s="23"/>
+      <c r="BA7" s="23"/>
+      <c r="BB7" s="23"/>
+      <c r="BC7" s="23"/>
+      <c r="BD7" s="23"/>
+      <c r="BE7" s="23"/>
+      <c r="BF7" s="23"/>
+      <c r="BG7" s="23"/>
+      <c r="BH7" s="23"/>
+      <c r="BI7" s="23"/>
+      <c r="BJ7" s="23"/>
+      <c r="BK7" s="23"/>
     </row>
     <row r="8" spans="2:63" x14ac:dyDescent="0.4">
       <c r="B8" s="3" t="s">
         <v>53</v>
       </c>
+      <c r="C8" s="23"/>
+      <c r="D8" s="23"/>
+      <c r="E8" s="23"/>
+      <c r="F8" s="23"/>
+      <c r="G8" s="23"/>
+      <c r="H8" s="23"/>
+      <c r="I8" s="23"/>
+      <c r="J8" s="23"/>
+      <c r="K8" s="23"/>
+      <c r="L8" s="23"/>
+      <c r="M8" s="23"/>
+      <c r="N8" s="23"/>
+      <c r="O8" s="23"/>
+      <c r="P8" s="23"/>
+      <c r="Q8" s="23"/>
+      <c r="R8" s="23"/>
+      <c r="S8" s="23"/>
+      <c r="T8" s="23"/>
+      <c r="U8" s="23"/>
+      <c r="V8" s="23"/>
+      <c r="W8" s="23"/>
+      <c r="X8" s="23"/>
+      <c r="Y8" s="23"/>
+      <c r="Z8" s="23"/>
+      <c r="AA8" s="23"/>
+      <c r="AB8" s="23"/>
+      <c r="AC8" s="23"/>
+      <c r="AD8" s="23"/>
+      <c r="AE8" s="23"/>
+      <c r="AF8" s="23"/>
+      <c r="AG8" s="23"/>
+      <c r="AH8" s="23"/>
+      <c r="AI8" s="23"/>
+      <c r="AJ8" s="23"/>
+      <c r="AK8" s="23"/>
+      <c r="AL8" s="23"/>
+      <c r="AM8" s="23"/>
+      <c r="AN8" s="23"/>
+      <c r="AO8" s="23"/>
+      <c r="AP8" s="23"/>
+      <c r="AQ8" s="23"/>
+      <c r="AR8" s="23"/>
+      <c r="AS8" s="23"/>
+      <c r="AT8" s="23"/>
+      <c r="AU8" s="23"/>
+      <c r="AV8" s="23"/>
+      <c r="AW8" s="23"/>
+      <c r="AX8" s="23"/>
+      <c r="AY8" s="23"/>
+      <c r="AZ8" s="23"/>
+      <c r="BA8" s="23"/>
+      <c r="BB8" s="23"/>
+      <c r="BC8" s="23"/>
+      <c r="BD8" s="23"/>
+      <c r="BE8" s="23"/>
+      <c r="BF8" s="23"/>
+      <c r="BG8" s="23"/>
+      <c r="BH8" s="23"/>
+      <c r="BI8" s="23"/>
+      <c r="BJ8" s="23"/>
+      <c r="BK8" s="23"/>
     </row>
     <row r="9" spans="2:63" x14ac:dyDescent="0.4">
       <c r="B9" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="G9" t="s">
+      <c r="G9" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="H9" t="s">
+      <c r="H9" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="I9" t="s">
+      <c r="I9" s="23" t="s">
         <v>248</v>
       </c>
-      <c r="J9" t="s">
+      <c r="J9" s="23" t="s">
         <v>249</v>
       </c>
-      <c r="K9" t="s">
+      <c r="K9" s="23" t="s">
         <v>250</v>
       </c>
-      <c r="L9" t="s">
+      <c r="L9" s="23" t="s">
         <v>251</v>
       </c>
-      <c r="M9" t="s">
+      <c r="M9" s="23" t="s">
         <v>252</v>
       </c>
-      <c r="N9" t="s">
+      <c r="N9" s="23" t="s">
         <v>253</v>
       </c>
-      <c r="O9" t="s">
+      <c r="O9" s="23" t="s">
         <v>254</v>
       </c>
-      <c r="P9" t="s">
+      <c r="P9" s="23" t="s">
         <v>255</v>
       </c>
-      <c r="Q9" t="s">
+      <c r="Q9" s="23" t="s">
         <v>256</v>
       </c>
-      <c r="R9" t="s">
+      <c r="R9" s="23" t="s">
         <v>257</v>
       </c>
-      <c r="S9" t="s">
+      <c r="S9" s="23" t="s">
         <v>258</v>
       </c>
-      <c r="T9" t="s">
+      <c r="T9" s="23" t="s">
         <v>259</v>
       </c>
-      <c r="U9" t="s">
+      <c r="U9" s="23" t="s">
         <v>260</v>
       </c>
-      <c r="V9" t="s">
+      <c r="V9" s="23" t="s">
         <v>261</v>
       </c>
-      <c r="W9" t="s">
+      <c r="W9" s="23" t="s">
         <v>262</v>
       </c>
-      <c r="X9" t="s">
+      <c r="X9" s="23" t="s">
         <v>263</v>
       </c>
-      <c r="Y9" t="s">
+      <c r="Y9" s="23" t="s">
         <v>264</v>
       </c>
-      <c r="Z9" t="s">
+      <c r="Z9" s="23" t="s">
         <v>265</v>
       </c>
-      <c r="AA9" t="s">
+      <c r="AA9" s="23" t="s">
         <v>266</v>
       </c>
-      <c r="AB9" t="s">
+      <c r="AB9" s="23" t="s">
         <v>267</v>
       </c>
-      <c r="AC9" t="s">
+      <c r="AC9" s="23" t="s">
         <v>268</v>
       </c>
-      <c r="AD9" t="s">
+      <c r="AD9" s="23" t="s">
         <v>269</v>
       </c>
-      <c r="AE9" t="s">
+      <c r="AE9" s="23" t="s">
         <v>270</v>
       </c>
-      <c r="AF9" t="s">
+      <c r="AF9" s="23" t="s">
         <v>271</v>
       </c>
-      <c r="AG9" t="s">
+      <c r="AG9" s="23" t="s">
         <v>272</v>
       </c>
-      <c r="AH9" t="s">
+      <c r="AH9" s="23" t="s">
         <v>273</v>
       </c>
-      <c r="AI9" t="s">
+      <c r="AI9" s="23" t="s">
         <v>274</v>
       </c>
-      <c r="AJ9" t="s">
+      <c r="AJ9" s="23" t="s">
         <v>275</v>
       </c>
-      <c r="AK9" t="s">
+      <c r="AK9" s="23" t="s">
         <v>276</v>
       </c>
-      <c r="AL9" t="s">
+      <c r="AL9" s="23" t="s">
         <v>277</v>
       </c>
-      <c r="AM9" t="s">
+      <c r="AM9" s="23" t="s">
         <v>278</v>
       </c>
-      <c r="AN9" t="s">
+      <c r="AN9" s="23" t="s">
         <v>279</v>
       </c>
-      <c r="AO9" t="s">
+      <c r="AO9" s="23" t="s">
         <v>280</v>
       </c>
-      <c r="AP9" t="s">
+      <c r="AP9" s="23" t="s">
         <v>281</v>
       </c>
-      <c r="AQ9" t="s">
+      <c r="AQ9" s="23" t="s">
         <v>282</v>
       </c>
-      <c r="AR9" t="s">
+      <c r="AR9" s="23" t="s">
         <v>283</v>
       </c>
-      <c r="AS9" t="s">
+      <c r="AS9" s="23" t="s">
         <v>284</v>
       </c>
-      <c r="AT9" t="s">
+      <c r="AT9" s="23" t="s">
         <v>285</v>
       </c>
-      <c r="AU9" t="s">
+      <c r="AU9" s="23" t="s">
         <v>286</v>
       </c>
-      <c r="AV9" t="s">
+      <c r="AV9" s="23" t="s">
         <v>287</v>
       </c>
-      <c r="AW9" t="s">
+      <c r="AW9" s="23" t="s">
         <v>288</v>
       </c>
-      <c r="AX9" t="s">
+      <c r="AX9" s="23" t="s">
         <v>289</v>
       </c>
-      <c r="AY9" t="s">
+      <c r="AY9" s="23" t="s">
         <v>290</v>
       </c>
-      <c r="AZ9" t="s">
+      <c r="AZ9" s="23" t="s">
         <v>291</v>
       </c>
-      <c r="BA9" t="s">
+      <c r="BA9" s="23" t="s">
         <v>654</v>
       </c>
-      <c r="BB9" t="s">
+      <c r="BB9" s="23" t="s">
         <v>655</v>
       </c>
-      <c r="BC9" t="s">
+      <c r="BC9" s="23" t="s">
         <v>656</v>
       </c>
-      <c r="BD9" t="s">
+      <c r="BD9" s="23" t="s">
         <v>657</v>
       </c>
-      <c r="BE9" t="s">
+      <c r="BE9" s="23" t="s">
         <v>658</v>
       </c>
-      <c r="BF9" t="s">
+      <c r="BF9" s="23" t="s">
         <v>659</v>
       </c>
-      <c r="BG9" t="s">
+      <c r="BG9" s="23" t="s">
         <v>660</v>
       </c>
-      <c r="BH9" t="s">
+      <c r="BH9" s="23" t="s">
         <v>661</v>
       </c>
-      <c r="BI9" t="s">
+      <c r="BI9" s="23" t="s">
         <v>662</v>
       </c>
-      <c r="BJ9" t="s">
+      <c r="BJ9" s="23" t="s">
         <v>663</v>
       </c>
-      <c r="BK9" t="s">
+      <c r="BK9" s="23" t="s">
         <v>664</v>
       </c>
     </row>
